--- a/examples/Agilent/ใบสั่งงาน JOB 2.xlsx
+++ b/examples/Agilent/ใบสั่งงาน JOB 2.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\Agilent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E973C3-DD7C-4E8D-A086-5C1587006CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B754DE-D995-4E34-93D7-51B598228557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="480" windowWidth="28800" windowHeight="15150" tabRatio="958" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
+    <workbookView xWindow="-25035" yWindow="2175" windowWidth="23040" windowHeight="12120" tabRatio="958" activeTab="3" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="ใบงาน Agilent_JOB 2.1" sheetId="22" r:id="rId1"/>
     <sheet name="ใบงาน Agilent_JOB 2.2" sheetId="23" r:id="rId2"/>
     <sheet name="A2-QC ถุง" sheetId="24" r:id="rId3"/>
-    <sheet name="P2-QCกล่อง" sheetId="26" r:id="rId4"/>
+    <sheet name="P2-QC กล่อง" sheetId="26" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'ใบงาน Agilent_JOB 2.1'!$A$1:$O$50</definedName>
@@ -1439,12 +1439,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="23" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1493,55 +1538,28 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1559,31 +1577,190 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1595,200 +1772,23 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2658,90 +2658,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="114"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A5" s="98"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
+      <c r="A5" s="114"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="114"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
@@ -2903,48 +2903,48 @@
       <c r="O14" s="95"/>
     </row>
     <row r="15" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="116" t="s">
+      <c r="B15" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="132" t="s">
+      <c r="E15" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="99" t="s">
+      <c r="F15" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="114" t="s">
+      <c r="H15" s="129" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="86"/>
-      <c r="K15" s="115"/>
+      <c r="K15" s="130"/>
       <c r="L15" s="87"/>
       <c r="M15" s="87"/>
       <c r="N15" s="87"/>
       <c r="O15" s="87"/>
     </row>
     <row r="16" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="116"/>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="114"/>
+      <c r="A16" s="102"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="129"/>
       <c r="J16" s="86"/>
-      <c r="K16" s="115"/>
+      <c r="K16" s="130"/>
       <c r="L16" s="87"/>
       <c r="M16" s="87"/>
       <c r="N16" s="87"/>
@@ -2978,7 +2978,7 @@
         <f>G17*0.00328/F17</f>
         <v>32.967936000000002</v>
       </c>
-      <c r="K17" s="129" t="s">
+      <c r="K17" s="99" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="47"/>
@@ -3000,7 +3000,7 @@
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
       <c r="J18" s="17"/>
-      <c r="K18" s="129"/>
+      <c r="K18" s="99"/>
       <c r="L18" s="47"/>
       <c r="M18" s="32"/>
       <c r="N18" s="46"/>
@@ -3179,45 +3179,45 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="117" t="s">
+      <c r="B28" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="116" t="s">
+      <c r="C28" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="116" t="s">
+      <c r="D28" s="102" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="88"/>
-      <c r="F28" s="130" t="s">
+      <c r="F28" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="G28" s="99" t="s">
+      <c r="G28" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="99" t="s">
+      <c r="H28" s="98"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99" t="s">
+      <c r="L28" s="98"/>
+      <c r="M28" s="98"/>
+      <c r="N28" s="98" t="s">
         <v>68</v>
       </c>
       <c r="O28" s="90"/>
     </row>
     <row r="29" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="118"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
       <c r="E29" s="91"/>
-      <c r="F29" s="131"/>
+      <c r="F29" s="101"/>
       <c r="G29" s="84" t="s">
         <v>73</v>
       </c>
@@ -3239,24 +3239,24 @@
       <c r="M29" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="99"/>
+      <c r="N29" s="98"/>
       <c r="O29" s="90"/>
     </row>
     <row r="30" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="111">
+      <c r="A30" s="126">
         <v>2.1</v>
       </c>
-      <c r="B30" s="101" t="s">
+      <c r="B30" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="104" t="s">
+      <c r="C30" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="107">
+      <c r="D30" s="122">
         <v>2</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="104">
+      <c r="F30" s="119">
         <f>N8*D30</f>
         <v>9000</v>
       </c>
@@ -3264,7 +3264,7 @@
       <c r="H30" s="50"/>
       <c r="I30" s="50"/>
       <c r="J30" s="51"/>
-      <c r="K30" s="100" t="s">
+      <c r="K30" s="115" t="s">
         <v>56</v>
       </c>
       <c r="L30" s="10"/>
@@ -3273,119 +3273,119 @@
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="108"/>
+      <c r="A31" s="127"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="120"/>
+      <c r="D31" s="123"/>
       <c r="E31" s="22"/>
-      <c r="F31" s="105"/>
+      <c r="F31" s="120"/>
       <c r="G31" s="50"/>
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="51"/>
-      <c r="K31" s="100"/>
+      <c r="K31" s="115"/>
       <c r="L31" s="11"/>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="112"/>
-      <c r="B32" s="102"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="108"/>
+      <c r="A32" s="127"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="120"/>
+      <c r="D32" s="123"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="105"/>
+      <c r="F32" s="120"/>
       <c r="G32" s="50"/>
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
       <c r="J32" s="51"/>
-      <c r="K32" s="100"/>
+      <c r="K32" s="115"/>
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="112"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="108"/>
+      <c r="A33" s="127"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="123"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="105"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="50"/>
       <c r="H33" s="50"/>
       <c r="I33" s="50"/>
       <c r="J33" s="51"/>
-      <c r="K33" s="100"/>
+      <c r="K33" s="115"/>
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
       <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="112"/>
-      <c r="B34" s="102"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="108"/>
+      <c r="A34" s="127"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="120"/>
+      <c r="D34" s="123"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="105"/>
+      <c r="F34" s="120"/>
       <c r="G34" s="50"/>
       <c r="H34" s="50"/>
       <c r="I34" s="50"/>
       <c r="J34" s="51"/>
-      <c r="K34" s="100"/>
+      <c r="K34" s="115"/>
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="112"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="108"/>
+      <c r="A35" s="127"/>
+      <c r="B35" s="117"/>
+      <c r="C35" s="120"/>
+      <c r="D35" s="123"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="105"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="50"/>
       <c r="H35" s="50"/>
       <c r="I35" s="50"/>
       <c r="J35" s="51"/>
-      <c r="K35" s="100"/>
+      <c r="K35" s="115"/>
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="112"/>
-      <c r="B36" s="102"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="108"/>
+      <c r="A36" s="127"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="120"/>
+      <c r="D36" s="123"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="105"/>
+      <c r="F36" s="120"/>
       <c r="G36" s="50"/>
       <c r="H36" s="50"/>
       <c r="I36" s="50"/>
       <c r="J36" s="51"/>
-      <c r="K36" s="100"/>
+      <c r="K36" s="115"/>
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="113"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="109"/>
+      <c r="A37" s="128"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="121"/>
+      <c r="D37" s="124"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="106"/>
+      <c r="F37" s="121"/>
       <c r="G37" s="50"/>
       <c r="H37" s="50"/>
       <c r="I37" s="50"/>
       <c r="J37" s="51"/>
-      <c r="K37" s="100"/>
+      <c r="K37" s="115"/>
       <c r="L37" s="22"/>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -3423,72 +3423,72 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="121" t="s">
+      <c r="A41" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="121" t="s">
+      <c r="B41" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="121" t="s">
+      <c r="C41" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="124" t="s">
+      <c r="D41" s="109" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="27"/>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="124" t="s">
+      <c r="H41" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="I41" s="124" t="s">
+      <c r="I41" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="124" t="s">
+      <c r="J41" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="K41" s="124" t="s">
+      <c r="K41" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="L41" s="119" t="s">
+      <c r="L41" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="127"/>
-      <c r="N41" s="119" t="s">
+      <c r="M41" s="112"/>
+      <c r="N41" s="104" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="122"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="122"/>
-      <c r="D42" s="125"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="120"/>
-      <c r="M42" s="128"/>
-      <c r="N42" s="120"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="107"/>
+      <c r="D42" s="110"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="110"/>
+      <c r="I42" s="110"/>
+      <c r="J42" s="110"/>
+      <c r="K42" s="110"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="113"/>
+      <c r="N42" s="105"/>
     </row>
     <row r="43" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="123"/>
-      <c r="B43" s="123"/>
-      <c r="C43" s="123"/>
-      <c r="D43" s="126"/>
+      <c r="A43" s="108"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="111"/>
       <c r="E43" s="28"/>
-      <c r="F43" s="123"/>
-      <c r="G43" s="123"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="111"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="111"/>
+      <c r="K43" s="111"/>
       <c r="L43" s="29" t="s">
         <v>23</v>
       </c>
@@ -3708,27 +3708,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="K41:K43"/>
-    <mergeCell ref="L41:M42"/>
     <mergeCell ref="A1:N5"/>
     <mergeCell ref="N28:N29"/>
     <mergeCell ref="K30:K37"/>
@@ -3745,6 +3724,27 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="D28:D29"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="K41:K43"/>
+    <mergeCell ref="L41:M42"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -3775,86 +3775,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
     </row>
     <row r="2" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
     </row>
     <row r="3" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="114"/>
     </row>
     <row r="4" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
     </row>
     <row r="5" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A5" s="98"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
+      <c r="A5" s="114"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="114"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="4" t="s">
@@ -4012,44 +4012,44 @@
       <c r="O14" s="96"/>
     </row>
     <row r="15" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="142" t="s">
+      <c r="E15" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="140" t="s">
+      <c r="F15" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="130" t="s">
+      <c r="H15" s="100" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="86"/>
-      <c r="K15" s="115"/>
+      <c r="K15" s="130"/>
     </row>
     <row r="16" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="116"/>
-      <c r="B16" s="118"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="137"/>
+      <c r="A16" s="102"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="143"/>
       <c r="J16" s="86"/>
-      <c r="K16" s="115"/>
+      <c r="K16" s="130"/>
     </row>
     <row r="17" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="34">
@@ -4079,7 +4079,7 @@
         <f>G17*0.00328/F17</f>
         <v>35.666063999999999</v>
       </c>
-      <c r="K17" s="129" t="s">
+      <c r="K17" s="99" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="7"/>
@@ -4098,7 +4098,7 @@
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
       <c r="J18" s="17"/>
-      <c r="K18" s="129"/>
+      <c r="K18" s="99"/>
       <c r="L18" s="7"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -4270,45 +4270,45 @@
       <c r="O27" s="17"/>
     </row>
     <row r="28" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="117" t="s">
+      <c r="B28" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="116" t="s">
+      <c r="C28" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="116" t="s">
+      <c r="D28" s="102" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="88"/>
-      <c r="F28" s="130" t="s">
+      <c r="F28" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="G28" s="99" t="s">
+      <c r="G28" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="99" t="s">
+      <c r="H28" s="98"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99" t="s">
+      <c r="L28" s="98"/>
+      <c r="M28" s="98"/>
+      <c r="N28" s="98" t="s">
         <v>68</v>
       </c>
       <c r="O28" s="90"/>
     </row>
     <row r="29" spans="1:15" s="85" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="118"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
       <c r="E29" s="91"/>
-      <c r="F29" s="131"/>
+      <c r="F29" s="101"/>
       <c r="G29" s="84" t="s">
         <v>73</v>
       </c>
@@ -4330,24 +4330,24 @@
       <c r="M29" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="99"/>
+      <c r="N29" s="98"/>
       <c r="O29" s="90"/>
     </row>
     <row r="30" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="111">
+      <c r="A30" s="126">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B30" s="101" t="s">
+      <c r="B30" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="133" t="s">
+      <c r="C30" s="139" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="107">
+      <c r="D30" s="122">
         <v>1</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="104">
+      <c r="F30" s="119">
         <f>N8*D30</f>
         <v>4500</v>
       </c>
@@ -4355,7 +4355,7 @@
       <c r="H30" s="50"/>
       <c r="I30" s="50"/>
       <c r="J30" s="51"/>
-      <c r="K30" s="100" t="s">
+      <c r="K30" s="115" t="s">
         <v>59</v>
       </c>
       <c r="L30" s="10"/>
@@ -4364,119 +4364,119 @@
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="108"/>
+      <c r="A31" s="127"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="123"/>
       <c r="E31" s="22"/>
-      <c r="F31" s="105"/>
+      <c r="F31" s="120"/>
       <c r="G31" s="50"/>
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="51"/>
-      <c r="K31" s="100"/>
+      <c r="K31" s="115"/>
       <c r="L31" s="11"/>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="112"/>
-      <c r="B32" s="102"/>
-      <c r="C32" s="134"/>
-      <c r="D32" s="108"/>
+      <c r="A32" s="127"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="123"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="105"/>
+      <c r="F32" s="120"/>
       <c r="G32" s="50"/>
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
       <c r="J32" s="51"/>
-      <c r="K32" s="100"/>
+      <c r="K32" s="115"/>
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
       <c r="N32" s="22"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="112"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="108"/>
+      <c r="A33" s="127"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="123"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="105"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="50"/>
       <c r="H33" s="50"/>
       <c r="I33" s="50"/>
       <c r="J33" s="51"/>
-      <c r="K33" s="100"/>
+      <c r="K33" s="115"/>
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
       <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="112"/>
-      <c r="B34" s="102"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="108"/>
+      <c r="A34" s="127"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="123"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="105"/>
+      <c r="F34" s="120"/>
       <c r="G34" s="50"/>
       <c r="H34" s="50"/>
       <c r="I34" s="50"/>
       <c r="J34" s="51"/>
-      <c r="K34" s="100"/>
+      <c r="K34" s="115"/>
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="112"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="134"/>
-      <c r="D35" s="108"/>
+      <c r="A35" s="127"/>
+      <c r="B35" s="117"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="123"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="105"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="50"/>
       <c r="H35" s="50"/>
       <c r="I35" s="50"/>
       <c r="J35" s="51"/>
-      <c r="K35" s="100"/>
+      <c r="K35" s="115"/>
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="112"/>
-      <c r="B36" s="102"/>
-      <c r="C36" s="134"/>
-      <c r="D36" s="108"/>
+      <c r="A36" s="127"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="123"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="105"/>
+      <c r="F36" s="120"/>
       <c r="G36" s="50"/>
       <c r="H36" s="50"/>
       <c r="I36" s="50"/>
       <c r="J36" s="51"/>
-      <c r="K36" s="100"/>
+      <c r="K36" s="115"/>
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" s="16" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="113"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="135"/>
-      <c r="D37" s="109"/>
+      <c r="A37" s="128"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="141"/>
+      <c r="D37" s="124"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="106"/>
+      <c r="F37" s="121"/>
       <c r="G37" s="50"/>
       <c r="H37" s="50"/>
       <c r="I37" s="50"/>
       <c r="J37" s="51"/>
-      <c r="K37" s="100"/>
+      <c r="K37" s="115"/>
       <c r="L37" s="22"/>
       <c r="M37" s="22"/>
       <c r="N37" s="22"/>
@@ -4516,74 +4516,74 @@
       <c r="O40" s="17"/>
     </row>
     <row r="41" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="121" t="s">
+      <c r="A41" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="121" t="s">
+      <c r="B41" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="121" t="s">
+      <c r="C41" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="119" t="s">
+      <c r="D41" s="104" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="27"/>
-      <c r="F41" s="121" t="s">
+      <c r="F41" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="121" t="s">
+      <c r="G41" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="124" t="s">
+      <c r="H41" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="I41" s="124" t="s">
+      <c r="I41" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="124" t="s">
+      <c r="J41" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="K41" s="124" t="s">
+      <c r="K41" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="L41" s="119" t="s">
+      <c r="L41" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="127"/>
-      <c r="N41" s="138" t="s">
+      <c r="M41" s="112"/>
+      <c r="N41" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="138"/>
+      <c r="O41" s="137"/>
     </row>
     <row r="42" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="122"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="122"/>
-      <c r="D42" s="139"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="120"/>
-      <c r="M42" s="128"/>
-      <c r="N42" s="138"/>
-      <c r="O42" s="138"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="107"/>
+      <c r="D42" s="138"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="110"/>
+      <c r="I42" s="110"/>
+      <c r="J42" s="110"/>
+      <c r="K42" s="110"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="113"/>
+      <c r="N42" s="137"/>
+      <c r="O42" s="137"/>
     </row>
     <row r="43" spans="1:15" s="15" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="123"/>
-      <c r="B43" s="123"/>
-      <c r="C43" s="123"/>
-      <c r="D43" s="120"/>
+      <c r="A43" s="108"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="105"/>
       <c r="E43" s="28"/>
-      <c r="F43" s="123"/>
-      <c r="G43" s="123"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="111"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="111"/>
+      <c r="K43" s="111"/>
       <c r="L43" s="29" t="s">
         <v>23</v>
       </c>
@@ -4862,27 +4862,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="N41:O42"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="K41:K43"/>
-    <mergeCell ref="L41:M42"/>
     <mergeCell ref="A1:N5"/>
     <mergeCell ref="N28:N29"/>
     <mergeCell ref="K30:K37"/>
@@ -4899,6 +4878,27 @@
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="F28:F29"/>
+    <mergeCell ref="N41:O42"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="K41:K43"/>
+    <mergeCell ref="L41:M42"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -4919,195 +4919,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
       <c r="W1" s="56"/>
       <c r="X1" s="56"/>
       <c r="Y1" s="56"/>
       <c r="Z1" s="56"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="201"/>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="201"/>
-      <c r="K2" s="201"/>
-      <c r="L2" s="201"/>
-      <c r="M2" s="201"/>
-      <c r="N2" s="201"/>
-      <c r="O2" s="201"/>
-      <c r="P2" s="201"/>
-      <c r="Q2" s="201"/>
-      <c r="R2" s="201"/>
-      <c r="S2" s="201"/>
-      <c r="T2" s="201"/>
-      <c r="U2" s="201"/>
-      <c r="V2" s="201"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
       <c r="W2" s="56"/>
       <c r="X2" s="56"/>
       <c r="Y2" s="56"/>
       <c r="Z2" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="201"/>
-      <c r="B3" s="201"/>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
-      <c r="L3" s="201"/>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
-      <c r="Q3" s="201"/>
-      <c r="R3" s="201"/>
-      <c r="S3" s="201"/>
-      <c r="T3" s="201"/>
-      <c r="U3" s="201"/>
-      <c r="V3" s="201"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="144"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="144"/>
+      <c r="S3" s="144"/>
+      <c r="T3" s="144"/>
+      <c r="U3" s="144"/>
+      <c r="V3" s="144"/>
       <c r="W3" s="56"/>
       <c r="X3" s="56"/>
       <c r="Y3" s="56"/>
       <c r="Z3" s="56"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="201"/>
-      <c r="B4" s="201"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="M4" s="201"/>
-      <c r="N4" s="201"/>
-      <c r="O4" s="201"/>
-      <c r="P4" s="201"/>
-      <c r="Q4" s="201"/>
-      <c r="R4" s="201"/>
-      <c r="S4" s="201"/>
-      <c r="T4" s="201"/>
-      <c r="U4" s="201"/>
-      <c r="V4" s="201"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="144"/>
+      <c r="Q4" s="144"/>
+      <c r="R4" s="144"/>
+      <c r="S4" s="144"/>
+      <c r="T4" s="144"/>
+      <c r="U4" s="144"/>
+      <c r="V4" s="144"/>
       <c r="W4" s="56"/>
       <c r="X4" s="56"/>
       <c r="Y4" s="56"/>
       <c r="Z4" s="56"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="201"/>
-      <c r="R5" s="201"/>
-      <c r="S5" s="201"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="201"/>
-      <c r="V5" s="201"/>
+      <c r="A5" s="144"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
+      <c r="R5" s="144"/>
+      <c r="S5" s="144"/>
+      <c r="T5" s="144"/>
+      <c r="U5" s="144"/>
+      <c r="V5" s="144"/>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="56"/>
       <c r="Z5" s="56"/>
     </row>
     <row r="6" spans="1:26" ht="30">
-      <c r="A6" s="209" t="s">
+      <c r="A6" s="153" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="209"/>
-      <c r="C6" s="209"/>
-      <c r="D6" s="209"/>
-      <c r="E6" s="209"/>
-      <c r="F6" s="209"/>
-      <c r="G6" s="209"/>
-      <c r="H6" s="209"/>
-      <c r="I6" s="209"/>
-      <c r="J6" s="209"/>
-      <c r="K6" s="209"/>
-      <c r="L6" s="209"/>
-      <c r="M6" s="209"/>
-      <c r="N6" s="209"/>
-      <c r="O6" s="209"/>
-      <c r="P6" s="209"/>
-      <c r="Q6" s="209"/>
-      <c r="R6" s="209"/>
-      <c r="S6" s="209"/>
-      <c r="T6" s="209"/>
-      <c r="U6" s="209"/>
-      <c r="V6" s="209"/>
-      <c r="W6" s="209"/>
-      <c r="X6" s="209"/>
-      <c r="Y6" s="209"/>
-      <c r="Z6" s="209"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153"/>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
+      <c r="W6" s="153"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
     </row>
     <row r="7" spans="1:26" s="7" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="154" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="210"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="55" t="s">
         <v>81</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
-      <c r="G7" s="212" t="str">
+      <c r="G7" s="156" t="str">
         <f>'ใบงาน Agilent_JOB 2.1'!F7</f>
         <v>xxxx</v>
       </c>
-      <c r="H7" s="212"/>
-      <c r="I7" s="212"/>
-      <c r="J7" s="212"/>
-      <c r="K7" s="212"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="156"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
@@ -5140,13 +5140,13 @@
       <c r="D8" s="54"/>
       <c r="E8" s="54"/>
       <c r="F8" s="54"/>
-      <c r="G8" s="211" t="str">
+      <c r="G8" s="155" t="str">
         <f>'ใบงาน Agilent_JOB 2.1'!F9</f>
         <v>K9801-60082</v>
       </c>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="211"/>
+      <c r="H8" s="155"/>
+      <c r="I8" s="155"/>
+      <c r="J8" s="155"/>
       <c r="K8" s="54"/>
       <c r="L8" s="54"/>
       <c r="M8" s="54"/>
@@ -5159,17 +5159,17 @@
       <c r="T8" s="54"/>
     </row>
     <row r="9" spans="1:26" s="7" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A9" s="210" t="s">
+      <c r="A9" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="210"/>
-      <c r="G9" s="211" t="str">
+      <c r="B9" s="154"/>
+      <c r="G9" s="155" t="str">
         <f>'ใบงาน Agilent_JOB 2.2'!F9</f>
         <v>K9801-60083</v>
       </c>
-      <c r="H9" s="211"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="211"/>
+      <c r="H9" s="155"/>
+      <c r="I9" s="155"/>
+      <c r="J9" s="155"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
@@ -5177,12 +5177,12 @@
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
-      <c r="S9" s="129" t="s">
+      <c r="S9" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="T9" s="129"/>
-      <c r="U9" s="129"/>
-      <c r="V9" s="129"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
     </row>
     <row r="10" spans="1:26" s="7" customFormat="1" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
@@ -5193,17 +5193,17 @@
         <v>4500</v>
       </c>
       <c r="C10" s="17"/>
-      <c r="D10" s="212" t="s">
+      <c r="D10" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="202" t="s">
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
       <c r="K10" s="55"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
@@ -5212,10 +5212,10 @@
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
-      <c r="S10" s="129"/>
-      <c r="T10" s="129"/>
-      <c r="U10" s="129"/>
-      <c r="V10" s="129"/>
+      <c r="S10" s="99"/>
+      <c r="T10" s="99"/>
+      <c r="U10" s="99"/>
+      <c r="V10" s="99"/>
     </row>
     <row r="11" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A11" s="17"/>
@@ -5224,12 +5224,12 @@
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
-      <c r="G11" s="202" t="s">
+      <c r="G11" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="202"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="202"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
@@ -5250,12 +5250,12 @@
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="202" t="s">
+      <c r="G12" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="202"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="202"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -5290,72 +5290,72 @@
       <c r="T13" s="17"/>
     </row>
     <row r="14" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="A14" s="203" t="s">
+      <c r="A14" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="203" t="s">
+      <c r="B14" s="146" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="194" t="s">
+      <c r="C14" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="194" t="s">
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="204"/>
-      <c r="K14" s="204"/>
-      <c r="L14" s="204"/>
-      <c r="M14" s="204"/>
-      <c r="N14" s="205"/>
-      <c r="O14" s="194" t="s">
+      <c r="J14" s="148"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="148"/>
+      <c r="M14" s="148"/>
+      <c r="N14" s="149"/>
+      <c r="O14" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="195"/>
-      <c r="S14" s="195"/>
-      <c r="T14" s="196"/>
-      <c r="U14" s="200" t="s">
+      <c r="P14" s="158"/>
+      <c r="Q14" s="158"/>
+      <c r="R14" s="158"/>
+      <c r="S14" s="158"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="163" t="s">
         <v>89</v>
       </c>
-      <c r="V14" s="200"/>
-      <c r="W14" s="200"/>
-      <c r="X14" s="200"/>
-      <c r="Y14" s="200"/>
-      <c r="Z14" s="200"/>
+      <c r="V14" s="163"/>
+      <c r="W14" s="163"/>
+      <c r="X14" s="163"/>
+      <c r="Y14" s="163"/>
+      <c r="Z14" s="163"/>
     </row>
     <row r="15" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="A15" s="121"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="207"/>
-      <c r="H15" s="208"/>
-      <c r="I15" s="206"/>
-      <c r="J15" s="207"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="208"/>
-      <c r="O15" s="197"/>
-      <c r="P15" s="198"/>
-      <c r="Q15" s="198"/>
-      <c r="R15" s="198"/>
-      <c r="S15" s="198"/>
-      <c r="T15" s="199"/>
-      <c r="U15" s="200"/>
-      <c r="V15" s="200"/>
-      <c r="W15" s="200"/>
-      <c r="X15" s="200"/>
-      <c r="Y15" s="200"/>
-      <c r="Z15" s="200"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="151"/>
+      <c r="M15" s="151"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="160"/>
+      <c r="P15" s="161"/>
+      <c r="Q15" s="161"/>
+      <c r="R15" s="161"/>
+      <c r="S15" s="161"/>
+      <c r="T15" s="162"/>
+      <c r="U15" s="163"/>
+      <c r="V15" s="163"/>
+      <c r="W15" s="163"/>
+      <c r="X15" s="163"/>
+      <c r="Y15" s="163"/>
+      <c r="Z15" s="163"/>
     </row>
     <row r="16" spans="1:26" s="60" customFormat="1" ht="35.700000000000003" customHeight="1">
       <c r="A16" s="58">
@@ -5364,184 +5364,184 @@
       <c r="B16" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-      <c r="F16" s="189"/>
-      <c r="G16" s="189"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="189" t="s">
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="189"/>
-      <c r="K16" s="189"/>
-      <c r="L16" s="189"/>
-      <c r="M16" s="189"/>
-      <c r="N16" s="189"/>
-      <c r="O16" s="189"/>
-      <c r="P16" s="189"/>
-      <c r="Q16" s="189"/>
-      <c r="R16" s="189"/>
-      <c r="S16" s="189"/>
-      <c r="T16" s="189"/>
-      <c r="U16" s="189"/>
-      <c r="V16" s="189"/>
-      <c r="W16" s="189"/>
-      <c r="X16" s="189"/>
-      <c r="Y16" s="189"/>
-      <c r="Z16" s="189"/>
+      <c r="J16" s="157"/>
+      <c r="K16" s="157"/>
+      <c r="L16" s="157"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="157"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="157"/>
+      <c r="Q16" s="157"/>
+      <c r="R16" s="157"/>
+      <c r="S16" s="157"/>
+      <c r="T16" s="157"/>
+      <c r="U16" s="157"/>
+      <c r="V16" s="157"/>
+      <c r="W16" s="157"/>
+      <c r="X16" s="157"/>
+      <c r="Y16" s="157"/>
+      <c r="Z16" s="157"/>
     </row>
     <row r="17" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="190">
+      <c r="A17" s="164">
         <v>2</v>
       </c>
       <c r="B17" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="189"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="189"/>
-      <c r="H17" s="189"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="189"/>
-      <c r="L17" s="189"/>
-      <c r="M17" s="189"/>
-      <c r="N17" s="189"/>
-      <c r="O17" s="189"/>
-      <c r="P17" s="189"/>
-      <c r="Q17" s="189"/>
-      <c r="R17" s="189"/>
-      <c r="S17" s="189"/>
-      <c r="T17" s="189"/>
-      <c r="U17" s="189"/>
-      <c r="V17" s="189"/>
-      <c r="W17" s="189"/>
-      <c r="X17" s="189"/>
-      <c r="Y17" s="189"/>
-      <c r="Z17" s="189"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="157"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="157"/>
+      <c r="Q17" s="157"/>
+      <c r="R17" s="157"/>
+      <c r="S17" s="157"/>
+      <c r="T17" s="157"/>
+      <c r="U17" s="157"/>
+      <c r="V17" s="157"/>
+      <c r="W17" s="157"/>
+      <c r="X17" s="157"/>
+      <c r="Y17" s="157"/>
+      <c r="Z17" s="157"/>
     </row>
     <row r="18" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A18" s="191"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="189"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="189"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="189"/>
-      <c r="L18" s="189"/>
-      <c r="M18" s="189"/>
-      <c r="N18" s="189"/>
-      <c r="O18" s="189"/>
-      <c r="P18" s="189"/>
-      <c r="Q18" s="189"/>
-      <c r="R18" s="189"/>
-      <c r="S18" s="189"/>
-      <c r="T18" s="189"/>
-      <c r="U18" s="189"/>
-      <c r="V18" s="189"/>
-      <c r="W18" s="189"/>
-      <c r="X18" s="189"/>
-      <c r="Y18" s="189"/>
-      <c r="Z18" s="189"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="157"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="157"/>
+      <c r="N18" s="157"/>
+      <c r="O18" s="157"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="157"/>
+      <c r="S18" s="157"/>
+      <c r="T18" s="157"/>
+      <c r="U18" s="157"/>
+      <c r="V18" s="157"/>
+      <c r="W18" s="157"/>
+      <c r="X18" s="157"/>
+      <c r="Y18" s="157"/>
+      <c r="Z18" s="157"/>
     </row>
     <row r="19" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A19" s="191"/>
+      <c r="A19" s="165"/>
       <c r="B19" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="189"/>
-      <c r="D19" s="189"/>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="189"/>
-      <c r="H19" s="189"/>
-      <c r="I19" s="189"/>
-      <c r="J19" s="189"/>
-      <c r="K19" s="189"/>
-      <c r="L19" s="189"/>
-      <c r="M19" s="189"/>
-      <c r="N19" s="189"/>
-      <c r="O19" s="189"/>
-      <c r="P19" s="189"/>
-      <c r="Q19" s="189"/>
-      <c r="R19" s="189"/>
-      <c r="S19" s="189"/>
-      <c r="T19" s="189"/>
-      <c r="U19" s="189"/>
-      <c r="V19" s="189"/>
-      <c r="W19" s="189"/>
-      <c r="X19" s="189"/>
-      <c r="Y19" s="189"/>
-      <c r="Z19" s="189"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="157"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="157"/>
+      <c r="K19" s="157"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="157"/>
+      <c r="O19" s="157"/>
+      <c r="P19" s="157"/>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="157"/>
+      <c r="S19" s="157"/>
+      <c r="T19" s="157"/>
+      <c r="U19" s="157"/>
+      <c r="V19" s="157"/>
+      <c r="W19" s="157"/>
+      <c r="X19" s="157"/>
+      <c r="Y19" s="157"/>
+      <c r="Z19" s="157"/>
     </row>
     <row r="20" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A20" s="191"/>
+      <c r="A20" s="165"/>
       <c r="B20" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="189"/>
-      <c r="D20" s="189"/>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="189"/>
-      <c r="L20" s="189"/>
-      <c r="M20" s="189"/>
-      <c r="N20" s="189"/>
-      <c r="O20" s="189"/>
-      <c r="P20" s="189"/>
-      <c r="Q20" s="189"/>
-      <c r="R20" s="189"/>
-      <c r="S20" s="189"/>
-      <c r="T20" s="189"/>
-      <c r="U20" s="189"/>
-      <c r="V20" s="189"/>
-      <c r="W20" s="189"/>
-      <c r="X20" s="189"/>
-      <c r="Y20" s="189"/>
-      <c r="Z20" s="189"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="157"/>
+      <c r="I20" s="157"/>
+      <c r="J20" s="157"/>
+      <c r="K20" s="157"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="157"/>
+      <c r="O20" s="157"/>
+      <c r="P20" s="157"/>
+      <c r="Q20" s="157"/>
+      <c r="R20" s="157"/>
+      <c r="S20" s="157"/>
+      <c r="T20" s="157"/>
+      <c r="U20" s="157"/>
+      <c r="V20" s="157"/>
+      <c r="W20" s="157"/>
+      <c r="X20" s="157"/>
+      <c r="Y20" s="157"/>
+      <c r="Z20" s="157"/>
     </row>
     <row r="21" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A21" s="192"/>
+      <c r="A21" s="166"/>
       <c r="B21" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="189"/>
-      <c r="D21" s="189"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="189"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="189"/>
-      <c r="L21" s="189"/>
-      <c r="M21" s="189"/>
-      <c r="N21" s="189"/>
-      <c r="O21" s="189"/>
-      <c r="P21" s="189"/>
-      <c r="Q21" s="189"/>
-      <c r="R21" s="189"/>
-      <c r="S21" s="189"/>
-      <c r="T21" s="189"/>
-      <c r="U21" s="189"/>
-      <c r="V21" s="189"/>
-      <c r="W21" s="189"/>
-      <c r="X21" s="189"/>
-      <c r="Y21" s="189"/>
-      <c r="Z21" s="189"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="157"/>
+      <c r="I21" s="157"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="157"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="157"/>
+      <c r="S21" s="157"/>
+      <c r="T21" s="157"/>
+      <c r="U21" s="157"/>
+      <c r="V21" s="157"/>
+      <c r="W21" s="157"/>
+      <c r="X21" s="157"/>
+      <c r="Y21" s="157"/>
+      <c r="Z21" s="157"/>
     </row>
     <row r="22" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
       <c r="A22" s="58">
@@ -5550,30 +5550,30 @@
       <c r="B22" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="189"/>
-      <c r="D22" s="189"/>
-      <c r="E22" s="189"/>
-      <c r="F22" s="189"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="189"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="189"/>
-      <c r="L22" s="189"/>
-      <c r="M22" s="189"/>
-      <c r="N22" s="189"/>
-      <c r="O22" s="189"/>
-      <c r="P22" s="189"/>
-      <c r="Q22" s="189"/>
-      <c r="R22" s="189"/>
-      <c r="S22" s="189"/>
-      <c r="T22" s="189"/>
-      <c r="U22" s="189"/>
-      <c r="V22" s="189"/>
-      <c r="W22" s="189"/>
-      <c r="X22" s="189"/>
-      <c r="Y22" s="189"/>
-      <c r="Z22" s="189"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="157"/>
+      <c r="O22" s="157"/>
+      <c r="P22" s="157"/>
+      <c r="Q22" s="157"/>
+      <c r="R22" s="157"/>
+      <c r="S22" s="157"/>
+      <c r="T22" s="157"/>
+      <c r="U22" s="157"/>
+      <c r="V22" s="157"/>
+      <c r="W22" s="157"/>
+      <c r="X22" s="157"/>
+      <c r="Y22" s="157"/>
+      <c r="Z22" s="157"/>
     </row>
     <row r="23" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
       <c r="A23" s="58">
@@ -5582,30 +5582,30 @@
       <c r="B23" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="189"/>
-      <c r="D23" s="189"/>
-      <c r="E23" s="189"/>
-      <c r="F23" s="189"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="189"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="189"/>
-      <c r="K23" s="189"/>
-      <c r="L23" s="189"/>
-      <c r="M23" s="189"/>
-      <c r="N23" s="189"/>
-      <c r="O23" s="189"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="189"/>
-      <c r="T23" s="189"/>
-      <c r="U23" s="189"/>
-      <c r="V23" s="189"/>
-      <c r="W23" s="189"/>
-      <c r="X23" s="189"/>
-      <c r="Y23" s="189"/>
-      <c r="Z23" s="189"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="157"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="157"/>
+      <c r="O23" s="157"/>
+      <c r="P23" s="157"/>
+      <c r="Q23" s="157"/>
+      <c r="R23" s="157"/>
+      <c r="S23" s="157"/>
+      <c r="T23" s="157"/>
+      <c r="U23" s="157"/>
+      <c r="V23" s="157"/>
+      <c r="W23" s="157"/>
+      <c r="X23" s="157"/>
+      <c r="Y23" s="157"/>
+      <c r="Z23" s="157"/>
     </row>
     <row r="24" spans="1:26" s="60" customFormat="1" ht="22.5" customHeight="1">
       <c r="A24" s="58">
@@ -5614,30 +5614,30 @@
       <c r="B24" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="189"/>
-      <c r="D24" s="189"/>
-      <c r="E24" s="189"/>
-      <c r="F24" s="189"/>
-      <c r="G24" s="189"/>
-      <c r="H24" s="189"/>
-      <c r="I24" s="189"/>
-      <c r="J24" s="189"/>
-      <c r="K24" s="189"/>
-      <c r="L24" s="189"/>
-      <c r="M24" s="189"/>
-      <c r="N24" s="189"/>
-      <c r="O24" s="189"/>
-      <c r="P24" s="189"/>
-      <c r="Q24" s="189"/>
-      <c r="R24" s="189"/>
-      <c r="S24" s="189"/>
-      <c r="T24" s="189"/>
-      <c r="U24" s="189"/>
-      <c r="V24" s="189"/>
-      <c r="W24" s="189"/>
-      <c r="X24" s="189"/>
-      <c r="Y24" s="189"/>
-      <c r="Z24" s="189"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="157"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="157"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="157"/>
+      <c r="J24" s="157"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="157"/>
+      <c r="P24" s="157"/>
+      <c r="Q24" s="157"/>
+      <c r="R24" s="157"/>
+      <c r="S24" s="157"/>
+      <c r="T24" s="157"/>
+      <c r="U24" s="157"/>
+      <c r="V24" s="157"/>
+      <c r="W24" s="157"/>
+      <c r="X24" s="157"/>
+      <c r="Y24" s="157"/>
+      <c r="Z24" s="157"/>
     </row>
     <row r="25" spans="1:26" s="60" customFormat="1" ht="20.7" customHeight="1">
       <c r="A25" s="58">
@@ -5646,256 +5646,256 @@
       <c r="B25" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="189"/>
-      <c r="D25" s="189"/>
-      <c r="E25" s="189"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="189"/>
-      <c r="H25" s="189"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="189"/>
-      <c r="L25" s="189"/>
-      <c r="M25" s="189"/>
-      <c r="N25" s="189"/>
-      <c r="O25" s="189"/>
-      <c r="P25" s="189"/>
-      <c r="Q25" s="189"/>
-      <c r="R25" s="189"/>
-      <c r="S25" s="189"/>
-      <c r="T25" s="189"/>
-      <c r="U25" s="189"/>
-      <c r="V25" s="189"/>
-      <c r="W25" s="189"/>
-      <c r="X25" s="189"/>
-      <c r="Y25" s="189"/>
-      <c r="Z25" s="189"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="157"/>
+      <c r="H25" s="157"/>
+      <c r="I25" s="157"/>
+      <c r="J25" s="157"/>
+      <c r="K25" s="157"/>
+      <c r="L25" s="157"/>
+      <c r="M25" s="157"/>
+      <c r="N25" s="157"/>
+      <c r="O25" s="157"/>
+      <c r="P25" s="157"/>
+      <c r="Q25" s="157"/>
+      <c r="R25" s="157"/>
+      <c r="S25" s="157"/>
+      <c r="T25" s="157"/>
+      <c r="U25" s="157"/>
+      <c r="V25" s="157"/>
+      <c r="W25" s="157"/>
+      <c r="X25" s="157"/>
+      <c r="Y25" s="157"/>
+      <c r="Z25" s="157"/>
     </row>
     <row r="26" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A26" s="6"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
+      <c r="C26" s="167"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
     </row>
     <row r="27" spans="1:26" s="7" customFormat="1" ht="15.6">
-      <c r="A27" s="193" t="s">
+      <c r="A27" s="168" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="193"/>
-      <c r="C27" s="193"/>
-      <c r="D27" s="193"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="193"/>
-      <c r="G27" s="193"/>
-      <c r="H27" s="193"/>
-      <c r="I27" s="193"/>
-      <c r="J27" s="193"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="168"/>
+      <c r="H27" s="168"/>
+      <c r="I27" s="168"/>
+      <c r="J27" s="168"/>
     </row>
     <row r="28" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A28" s="178" t="s">
+      <c r="A28" s="169" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="179"/>
-      <c r="C28" s="185" t="s">
+      <c r="B28" s="170"/>
+      <c r="C28" s="171" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="185"/>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="186" t="s">
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="172" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="187"/>
-      <c r="I28" s="187"/>
-      <c r="J28" s="188"/>
-      <c r="L28" s="183" t="s">
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="174"/>
+      <c r="L28" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="M28" s="183"/>
+      <c r="M28" s="176"/>
     </row>
     <row r="29" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A29" s="178" t="s">
+      <c r="A29" s="169" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="179"/>
-      <c r="C29" s="184">
+      <c r="B29" s="170"/>
+      <c r="C29" s="175">
         <v>10</v>
       </c>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184">
+      <c r="D29" s="175"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="175">
         <v>10</v>
       </c>
-      <c r="H29" s="184"/>
-      <c r="I29" s="184"/>
-      <c r="J29" s="184"/>
-      <c r="L29" s="183"/>
-      <c r="M29" s="183"/>
+      <c r="H29" s="175"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="175"/>
+      <c r="L29" s="176"/>
+      <c r="M29" s="176"/>
     </row>
     <row r="30" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A30" s="178" t="s">
+      <c r="A30" s="169" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="184">
+      <c r="B30" s="170"/>
+      <c r="C30" s="175">
         <v>20</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="184">
+      <c r="D30" s="175"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="175"/>
+      <c r="G30" s="175">
         <v>20</v>
       </c>
-      <c r="H30" s="184"/>
-      <c r="I30" s="184"/>
-      <c r="J30" s="184"/>
-      <c r="L30" s="183"/>
-      <c r="M30" s="183"/>
+      <c r="H30" s="175"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="175"/>
+      <c r="L30" s="176"/>
+      <c r="M30" s="176"/>
     </row>
     <row r="31" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A31" s="178" t="s">
+      <c r="A31" s="169" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="179"/>
-      <c r="C31" s="184">
+      <c r="B31" s="170"/>
+      <c r="C31" s="175">
         <v>30</v>
       </c>
-      <c r="D31" s="184"/>
-      <c r="E31" s="184"/>
-      <c r="F31" s="184"/>
-      <c r="G31" s="184">
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175">
         <v>30</v>
       </c>
-      <c r="H31" s="184"/>
-      <c r="I31" s="184"/>
-      <c r="J31" s="184"/>
-      <c r="L31" s="183"/>
-      <c r="M31" s="183"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="176"/>
     </row>
     <row r="32" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A32" s="178" t="s">
+      <c r="A32" s="169" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="179"/>
-      <c r="C32" s="180">
+      <c r="B32" s="170"/>
+      <c r="C32" s="177">
         <v>40</v>
       </c>
-      <c r="D32" s="181"/>
-      <c r="E32" s="181"/>
-      <c r="F32" s="182"/>
-      <c r="G32" s="180">
+      <c r="D32" s="178"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="177">
         <v>40</v>
       </c>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="182"/>
-      <c r="L32" s="183"/>
-      <c r="M32" s="183"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="179"/>
+      <c r="L32" s="176"/>
+      <c r="M32" s="176"/>
     </row>
     <row r="33" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A33" s="178" t="s">
+      <c r="A33" s="169" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="179"/>
-      <c r="C33" s="184">
+      <c r="B33" s="170"/>
+      <c r="C33" s="175">
         <v>50</v>
       </c>
-      <c r="D33" s="184"/>
-      <c r="E33" s="184"/>
-      <c r="F33" s="184"/>
-      <c r="G33" s="184">
+      <c r="D33" s="175"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="175"/>
+      <c r="G33" s="175">
         <v>50</v>
       </c>
-      <c r="H33" s="184"/>
-      <c r="I33" s="184"/>
-      <c r="J33" s="184"/>
-      <c r="L33" s="183"/>
-      <c r="M33" s="183"/>
+      <c r="H33" s="175"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="175"/>
+      <c r="L33" s="176"/>
+      <c r="M33" s="176"/>
     </row>
     <row r="34" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A34" s="178" t="s">
+      <c r="A34" s="169" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="179"/>
-      <c r="C34" s="184">
+      <c r="B34" s="170"/>
+      <c r="C34" s="175">
         <v>100</v>
       </c>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184">
+      <c r="D34" s="175"/>
+      <c r="E34" s="175"/>
+      <c r="F34" s="175"/>
+      <c r="G34" s="175">
         <v>100</v>
       </c>
-      <c r="H34" s="184"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="L34" s="183"/>
-      <c r="M34" s="183"/>
+      <c r="H34" s="175"/>
+      <c r="I34" s="175"/>
+      <c r="J34" s="175"/>
+      <c r="L34" s="176"/>
+      <c r="M34" s="176"/>
     </row>
     <row r="35" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A35" s="178" t="s">
+      <c r="A35" s="169" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="179"/>
-      <c r="C35" s="184">
+      <c r="B35" s="170"/>
+      <c r="C35" s="175">
         <v>200</v>
       </c>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184">
+      <c r="D35" s="175"/>
+      <c r="E35" s="175"/>
+      <c r="F35" s="175"/>
+      <c r="G35" s="175">
         <v>200</v>
       </c>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="L35" s="183"/>
-      <c r="M35" s="183"/>
+      <c r="H35" s="175"/>
+      <c r="I35" s="175"/>
+      <c r="J35" s="175"/>
+      <c r="L35" s="176"/>
+      <c r="M35" s="176"/>
     </row>
     <row r="36" spans="1:26" s="62" customFormat="1" ht="15">
-      <c r="A36" s="178" t="s">
+      <c r="A36" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="179"/>
-      <c r="C36" s="180" t="s">
+      <c r="B36" s="170"/>
+      <c r="C36" s="177" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="181"/>
-      <c r="E36" s="181"/>
-      <c r="F36" s="181"/>
-      <c r="G36" s="181"/>
-      <c r="H36" s="181"/>
-      <c r="I36" s="181"/>
-      <c r="J36" s="182"/>
-      <c r="L36" s="183"/>
-      <c r="M36" s="183"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178"/>
+      <c r="G36" s="178"/>
+      <c r="H36" s="178"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="179"/>
+      <c r="L36" s="176"/>
+      <c r="M36" s="176"/>
     </row>
     <row r="37" spans="1:26" s="62" customFormat="1" ht="15">
       <c r="A37" s="63"/>
-      <c r="L37" s="183"/>
-      <c r="M37" s="183"/>
+      <c r="L37" s="176"/>
+      <c r="M37" s="176"/>
     </row>
     <row r="38" spans="1:26" s="62" customFormat="1" ht="15">
       <c r="A38" s="63"/>
-      <c r="L38" s="183"/>
-      <c r="M38" s="183"/>
+      <c r="L38" s="176"/>
+      <c r="M38" s="176"/>
     </row>
     <row r="39" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A39" s="6"/>
-      <c r="L39" s="171"/>
-      <c r="M39" s="171"/>
+      <c r="L39" s="167"/>
+      <c r="M39" s="167"/>
     </row>
     <row r="40" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A40" s="6"/>
-      <c r="L40" s="171"/>
-      <c r="M40" s="171"/>
+      <c r="L40" s="167"/>
+      <c r="M40" s="167"/>
     </row>
     <row r="41" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A41" s="6"/>
-      <c r="L41" s="171"/>
-      <c r="M41" s="171"/>
+      <c r="L41" s="167"/>
+      <c r="M41" s="167"/>
     </row>
     <row r="42" spans="1:26" s="62" customFormat="1" ht="19.2" customHeight="1">
       <c r="A42" s="64" t="s">
@@ -5904,654 +5904,654 @@
       <c r="B42" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="172" t="s">
+      <c r="C42" s="180" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="173"/>
-      <c r="E42" s="173"/>
-      <c r="F42" s="173"/>
-      <c r="G42" s="173"/>
-      <c r="H42" s="173"/>
-      <c r="I42" s="173"/>
-      <c r="J42" s="173"/>
-      <c r="K42" s="173"/>
-      <c r="L42" s="173"/>
-      <c r="M42" s="173"/>
-      <c r="N42" s="174"/>
-      <c r="O42" s="175" t="s">
+      <c r="D42" s="181"/>
+      <c r="E42" s="181"/>
+      <c r="F42" s="181"/>
+      <c r="G42" s="181"/>
+      <c r="H42" s="181"/>
+      <c r="I42" s="181"/>
+      <c r="J42" s="181"/>
+      <c r="K42" s="181"/>
+      <c r="L42" s="181"/>
+      <c r="M42" s="181"/>
+      <c r="N42" s="182"/>
+      <c r="O42" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="P42" s="176"/>
-      <c r="Q42" s="176"/>
-      <c r="R42" s="176"/>
-      <c r="S42" s="177"/>
-      <c r="T42" s="175" t="s">
+      <c r="P42" s="184"/>
+      <c r="Q42" s="184"/>
+      <c r="R42" s="184"/>
+      <c r="S42" s="185"/>
+      <c r="T42" s="183" t="s">
         <v>117</v>
       </c>
-      <c r="U42" s="176"/>
-      <c r="V42" s="176"/>
-      <c r="W42" s="177"/>
-      <c r="X42" s="176" t="s">
+      <c r="U42" s="184"/>
+      <c r="V42" s="184"/>
+      <c r="W42" s="185"/>
+      <c r="X42" s="184" t="s">
         <v>118</v>
       </c>
-      <c r="Y42" s="176"/>
-      <c r="Z42" s="177"/>
+      <c r="Y42" s="184"/>
+      <c r="Z42" s="185"/>
     </row>
     <row r="43" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A43" s="168" t="s">
+      <c r="A43" s="192" t="s">
         <v>119</v>
       </c>
       <c r="B43" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="157" t="s">
+      <c r="C43" s="189" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="158"/>
-      <c r="E43" s="158"/>
-      <c r="F43" s="158"/>
-      <c r="G43" s="158"/>
-      <c r="H43" s="158"/>
-      <c r="I43" s="158"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="158"/>
-      <c r="L43" s="158"/>
-      <c r="M43" s="158"/>
-      <c r="N43" s="159"/>
-      <c r="O43" s="150" t="s">
+      <c r="D43" s="190"/>
+      <c r="E43" s="190"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="190"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="190"/>
+      <c r="J43" s="190"/>
+      <c r="K43" s="190"/>
+      <c r="L43" s="190"/>
+      <c r="M43" s="190"/>
+      <c r="N43" s="191"/>
+      <c r="O43" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P43" s="145"/>
-      <c r="Q43" s="145"/>
-      <c r="R43" s="145"/>
-      <c r="S43" s="146"/>
-      <c r="T43" s="150" t="s">
+      <c r="P43" s="187"/>
+      <c r="Q43" s="187"/>
+      <c r="R43" s="187"/>
+      <c r="S43" s="188"/>
+      <c r="T43" s="186" t="s">
         <v>123</v>
       </c>
-      <c r="U43" s="145"/>
-      <c r="V43" s="145"/>
-      <c r="W43" s="146"/>
-      <c r="X43" s="150">
+      <c r="U43" s="187"/>
+      <c r="V43" s="187"/>
+      <c r="W43" s="188"/>
+      <c r="X43" s="186">
         <v>1</v>
       </c>
-      <c r="Y43" s="145"/>
-      <c r="Z43" s="146"/>
+      <c r="Y43" s="187"/>
+      <c r="Z43" s="188"/>
     </row>
     <row r="44" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A44" s="169"/>
+      <c r="A44" s="193"/>
       <c r="B44" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="C44" s="157" t="s">
+      <c r="C44" s="189" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="158"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="158"/>
-      <c r="I44" s="158"/>
-      <c r="J44" s="158"/>
-      <c r="K44" s="158"/>
-      <c r="L44" s="158"/>
-      <c r="M44" s="158"/>
-      <c r="N44" s="159"/>
-      <c r="O44" s="150" t="s">
+      <c r="D44" s="190"/>
+      <c r="E44" s="190"/>
+      <c r="F44" s="190"/>
+      <c r="G44" s="190"/>
+      <c r="H44" s="190"/>
+      <c r="I44" s="190"/>
+      <c r="J44" s="190"/>
+      <c r="K44" s="190"/>
+      <c r="L44" s="190"/>
+      <c r="M44" s="190"/>
+      <c r="N44" s="191"/>
+      <c r="O44" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P44" s="145"/>
-      <c r="Q44" s="145"/>
-      <c r="R44" s="145"/>
-      <c r="S44" s="146"/>
-      <c r="T44" s="150" t="s">
+      <c r="P44" s="187"/>
+      <c r="Q44" s="187"/>
+      <c r="R44" s="187"/>
+      <c r="S44" s="188"/>
+      <c r="T44" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="U44" s="145"/>
-      <c r="V44" s="145"/>
-      <c r="W44" s="146"/>
-      <c r="X44" s="150">
+      <c r="U44" s="187"/>
+      <c r="V44" s="187"/>
+      <c r="W44" s="188"/>
+      <c r="X44" s="186">
         <v>1</v>
       </c>
-      <c r="Y44" s="145"/>
-      <c r="Z44" s="146"/>
+      <c r="Y44" s="187"/>
+      <c r="Z44" s="188"/>
     </row>
     <row r="45" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A45" s="169"/>
+      <c r="A45" s="193"/>
       <c r="B45" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="157" t="s">
+      <c r="C45" s="189" t="s">
         <v>128</v>
       </c>
-      <c r="D45" s="158"/>
-      <c r="E45" s="158"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="158"/>
-      <c r="I45" s="158"/>
-      <c r="J45" s="158"/>
-      <c r="K45" s="158"/>
-      <c r="L45" s="158"/>
-      <c r="M45" s="158"/>
-      <c r="N45" s="159"/>
-      <c r="O45" s="150" t="s">
+      <c r="D45" s="190"/>
+      <c r="E45" s="190"/>
+      <c r="F45" s="190"/>
+      <c r="G45" s="190"/>
+      <c r="H45" s="190"/>
+      <c r="I45" s="190"/>
+      <c r="J45" s="190"/>
+      <c r="K45" s="190"/>
+      <c r="L45" s="190"/>
+      <c r="M45" s="190"/>
+      <c r="N45" s="191"/>
+      <c r="O45" s="186" t="s">
         <v>129</v>
       </c>
-      <c r="P45" s="145"/>
-      <c r="Q45" s="145"/>
-      <c r="R45" s="145"/>
-      <c r="S45" s="146"/>
-      <c r="T45" s="150" t="s">
+      <c r="P45" s="187"/>
+      <c r="Q45" s="187"/>
+      <c r="R45" s="187"/>
+      <c r="S45" s="188"/>
+      <c r="T45" s="186" t="s">
         <v>130</v>
       </c>
-      <c r="U45" s="145"/>
-      <c r="V45" s="145"/>
-      <c r="W45" s="146"/>
-      <c r="X45" s="150">
+      <c r="U45" s="187"/>
+      <c r="V45" s="187"/>
+      <c r="W45" s="188"/>
+      <c r="X45" s="186">
         <v>6</v>
       </c>
-      <c r="Y45" s="145"/>
-      <c r="Z45" s="146"/>
+      <c r="Y45" s="187"/>
+      <c r="Z45" s="188"/>
     </row>
     <row r="46" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="169"/>
+      <c r="A46" s="193"/>
       <c r="B46" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="157" t="s">
+      <c r="C46" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="158"/>
-      <c r="I46" s="158"/>
-      <c r="J46" s="158"/>
-      <c r="K46" s="158"/>
-      <c r="L46" s="158"/>
-      <c r="M46" s="158"/>
-      <c r="N46" s="159"/>
-      <c r="O46" s="150" t="s">
+      <c r="D46" s="190"/>
+      <c r="E46" s="190"/>
+      <c r="F46" s="190"/>
+      <c r="G46" s="190"/>
+      <c r="H46" s="190"/>
+      <c r="I46" s="190"/>
+      <c r="J46" s="190"/>
+      <c r="K46" s="190"/>
+      <c r="L46" s="190"/>
+      <c r="M46" s="190"/>
+      <c r="N46" s="191"/>
+      <c r="O46" s="186" t="s">
         <v>133</v>
       </c>
-      <c r="P46" s="145"/>
-      <c r="Q46" s="145"/>
-      <c r="R46" s="145"/>
-      <c r="S46" s="146"/>
-      <c r="T46" s="150" t="s">
+      <c r="P46" s="187"/>
+      <c r="Q46" s="187"/>
+      <c r="R46" s="187"/>
+      <c r="S46" s="188"/>
+      <c r="T46" s="186" t="s">
         <v>134</v>
       </c>
-      <c r="U46" s="145"/>
-      <c r="V46" s="145"/>
-      <c r="W46" s="146"/>
-      <c r="X46" s="150">
+      <c r="U46" s="187"/>
+      <c r="V46" s="187"/>
+      <c r="W46" s="188"/>
+      <c r="X46" s="186">
         <v>6</v>
       </c>
-      <c r="Y46" s="145"/>
-      <c r="Z46" s="146"/>
+      <c r="Y46" s="187"/>
+      <c r="Z46" s="188"/>
     </row>
     <row r="47" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="170"/>
+      <c r="A47" s="194"/>
       <c r="B47" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="157" t="s">
+      <c r="C47" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="D47" s="158"/>
-      <c r="E47" s="158"/>
-      <c r="F47" s="158"/>
-      <c r="G47" s="158"/>
-      <c r="H47" s="158"/>
-      <c r="I47" s="158"/>
-      <c r="J47" s="158"/>
-      <c r="K47" s="158"/>
-      <c r="L47" s="158"/>
-      <c r="M47" s="158"/>
-      <c r="N47" s="159"/>
-      <c r="O47" s="150" t="s">
+      <c r="D47" s="190"/>
+      <c r="E47" s="190"/>
+      <c r="F47" s="190"/>
+      <c r="G47" s="190"/>
+      <c r="H47" s="190"/>
+      <c r="I47" s="190"/>
+      <c r="J47" s="190"/>
+      <c r="K47" s="190"/>
+      <c r="L47" s="190"/>
+      <c r="M47" s="190"/>
+      <c r="N47" s="191"/>
+      <c r="O47" s="186" t="s">
         <v>133</v>
       </c>
-      <c r="P47" s="145"/>
-      <c r="Q47" s="145"/>
-      <c r="R47" s="145"/>
-      <c r="S47" s="146"/>
-      <c r="T47" s="150" t="s">
+      <c r="P47" s="187"/>
+      <c r="Q47" s="187"/>
+      <c r="R47" s="187"/>
+      <c r="S47" s="188"/>
+      <c r="T47" s="186" t="s">
         <v>137</v>
       </c>
-      <c r="U47" s="145"/>
-      <c r="V47" s="145"/>
-      <c r="W47" s="146"/>
-      <c r="X47" s="150">
+      <c r="U47" s="187"/>
+      <c r="V47" s="187"/>
+      <c r="W47" s="188"/>
+      <c r="X47" s="186">
         <v>6</v>
       </c>
-      <c r="Y47" s="145"/>
-      <c r="Z47" s="146"/>
+      <c r="Y47" s="187"/>
+      <c r="Z47" s="188"/>
     </row>
     <row r="48" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="162" t="s">
+      <c r="A48" s="195" t="s">
         <v>138</v>
       </c>
       <c r="B48" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="157" t="s">
+      <c r="C48" s="189" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="158"/>
-      <c r="E48" s="158"/>
-      <c r="F48" s="158"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="158"/>
-      <c r="J48" s="158"/>
-      <c r="K48" s="158"/>
-      <c r="L48" s="158"/>
-      <c r="M48" s="158"/>
-      <c r="N48" s="159"/>
-      <c r="O48" s="150" t="s">
+      <c r="D48" s="190"/>
+      <c r="E48" s="190"/>
+      <c r="F48" s="190"/>
+      <c r="G48" s="190"/>
+      <c r="H48" s="190"/>
+      <c r="I48" s="190"/>
+      <c r="J48" s="190"/>
+      <c r="K48" s="190"/>
+      <c r="L48" s="190"/>
+      <c r="M48" s="190"/>
+      <c r="N48" s="191"/>
+      <c r="O48" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="P48" s="145"/>
-      <c r="Q48" s="145"/>
-      <c r="R48" s="145"/>
-      <c r="S48" s="146"/>
-      <c r="T48" s="150" t="s">
+      <c r="P48" s="187"/>
+      <c r="Q48" s="187"/>
+      <c r="R48" s="187"/>
+      <c r="S48" s="188"/>
+      <c r="T48" s="186" t="s">
         <v>45</v>
       </c>
-      <c r="U48" s="145"/>
-      <c r="V48" s="145"/>
-      <c r="W48" s="146"/>
-      <c r="X48" s="150">
+      <c r="U48" s="187"/>
+      <c r="V48" s="187"/>
+      <c r="W48" s="188"/>
+      <c r="X48" s="186">
         <v>2</v>
       </c>
-      <c r="Y48" s="145"/>
-      <c r="Z48" s="146"/>
+      <c r="Y48" s="187"/>
+      <c r="Z48" s="188"/>
     </row>
     <row r="49" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="164"/>
+      <c r="A49" s="196"/>
       <c r="B49" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C49" s="157" t="s">
+      <c r="C49" s="189" t="s">
         <v>142</v>
       </c>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="158"/>
-      <c r="L49" s="158"/>
-      <c r="M49" s="158"/>
-      <c r="N49" s="159"/>
-      <c r="O49" s="150" t="s">
+      <c r="D49" s="190"/>
+      <c r="E49" s="190"/>
+      <c r="F49" s="190"/>
+      <c r="G49" s="190"/>
+      <c r="H49" s="190"/>
+      <c r="I49" s="190"/>
+      <c r="J49" s="190"/>
+      <c r="K49" s="190"/>
+      <c r="L49" s="190"/>
+      <c r="M49" s="190"/>
+      <c r="N49" s="191"/>
+      <c r="O49" s="186" t="s">
         <v>63</v>
       </c>
-      <c r="P49" s="145"/>
-      <c r="Q49" s="145"/>
-      <c r="R49" s="145"/>
-      <c r="S49" s="146"/>
-      <c r="T49" s="150" t="s">
+      <c r="P49" s="187"/>
+      <c r="Q49" s="187"/>
+      <c r="R49" s="187"/>
+      <c r="S49" s="188"/>
+      <c r="T49" s="186" t="s">
         <v>47</v>
       </c>
-      <c r="U49" s="145"/>
-      <c r="V49" s="145"/>
-      <c r="W49" s="146"/>
-      <c r="X49" s="150">
+      <c r="U49" s="187"/>
+      <c r="V49" s="187"/>
+      <c r="W49" s="188"/>
+      <c r="X49" s="186">
         <v>1</v>
       </c>
-      <c r="Y49" s="145"/>
-      <c r="Z49" s="146"/>
+      <c r="Y49" s="187"/>
+      <c r="Z49" s="188"/>
     </row>
     <row r="50" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="162" t="s">
+      <c r="A50" s="195" t="s">
         <v>143</v>
       </c>
       <c r="B50" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="157" t="s">
+      <c r="C50" s="189" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="158"/>
-      <c r="E50" s="158"/>
-      <c r="F50" s="158"/>
-      <c r="G50" s="158"/>
-      <c r="H50" s="158"/>
-      <c r="I50" s="158"/>
-      <c r="J50" s="158"/>
-      <c r="K50" s="158"/>
-      <c r="L50" s="158"/>
-      <c r="M50" s="158"/>
-      <c r="N50" s="159"/>
-      <c r="O50" s="150" t="s">
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="191"/>
+      <c r="O50" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P50" s="145"/>
-      <c r="Q50" s="145"/>
-      <c r="R50" s="145"/>
-      <c r="S50" s="146"/>
-      <c r="T50" s="150" t="s">
+      <c r="P50" s="187"/>
+      <c r="Q50" s="187"/>
+      <c r="R50" s="187"/>
+      <c r="S50" s="188"/>
+      <c r="T50" s="186" t="s">
         <v>147</v>
       </c>
-      <c r="U50" s="145"/>
-      <c r="V50" s="145"/>
-      <c r="W50" s="146"/>
-      <c r="X50" s="150">
+      <c r="U50" s="187"/>
+      <c r="V50" s="187"/>
+      <c r="W50" s="188"/>
+      <c r="X50" s="186">
         <v>1</v>
       </c>
-      <c r="Y50" s="145"/>
-      <c r="Z50" s="146"/>
+      <c r="Y50" s="187"/>
+      <c r="Z50" s="188"/>
     </row>
     <row r="51" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="163"/>
+      <c r="A51" s="197"/>
       <c r="B51" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="C51" s="157" t="s">
+      <c r="C51" s="189" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="158"/>
-      <c r="E51" s="158"/>
-      <c r="F51" s="158"/>
-      <c r="G51" s="158"/>
-      <c r="H51" s="158"/>
-      <c r="I51" s="158"/>
-      <c r="J51" s="158"/>
-      <c r="K51" s="158"/>
-      <c r="L51" s="158"/>
-      <c r="M51" s="158"/>
-      <c r="N51" s="159"/>
-      <c r="O51" s="150" t="s">
+      <c r="D51" s="190"/>
+      <c r="E51" s="190"/>
+      <c r="F51" s="190"/>
+      <c r="G51" s="190"/>
+      <c r="H51" s="190"/>
+      <c r="I51" s="190"/>
+      <c r="J51" s="190"/>
+      <c r="K51" s="190"/>
+      <c r="L51" s="190"/>
+      <c r="M51" s="190"/>
+      <c r="N51" s="191"/>
+      <c r="O51" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P51" s="145"/>
-      <c r="Q51" s="145"/>
-      <c r="R51" s="145"/>
-      <c r="S51" s="146"/>
-      <c r="T51" s="150" t="s">
+      <c r="P51" s="187"/>
+      <c r="Q51" s="187"/>
+      <c r="R51" s="187"/>
+      <c r="S51" s="188"/>
+      <c r="T51" s="186" t="s">
         <v>150</v>
       </c>
-      <c r="U51" s="145"/>
-      <c r="V51" s="145"/>
-      <c r="W51" s="146"/>
-      <c r="X51" s="150">
+      <c r="U51" s="187"/>
+      <c r="V51" s="187"/>
+      <c r="W51" s="188"/>
+      <c r="X51" s="186">
         <v>4</v>
       </c>
-      <c r="Y51" s="145"/>
-      <c r="Z51" s="146"/>
+      <c r="Y51" s="187"/>
+      <c r="Z51" s="188"/>
     </row>
     <row r="52" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="163"/>
+      <c r="A52" s="197"/>
       <c r="B52" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="157" t="s">
+      <c r="C52" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="158"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="158"/>
-      <c r="G52" s="158"/>
-      <c r="H52" s="158"/>
-      <c r="I52" s="158"/>
-      <c r="J52" s="158"/>
-      <c r="K52" s="158"/>
-      <c r="L52" s="158"/>
-      <c r="M52" s="158"/>
-      <c r="N52" s="159"/>
-      <c r="O52" s="150" t="s">
+      <c r="D52" s="190"/>
+      <c r="E52" s="190"/>
+      <c r="F52" s="190"/>
+      <c r="G52" s="190"/>
+      <c r="H52" s="190"/>
+      <c r="I52" s="190"/>
+      <c r="J52" s="190"/>
+      <c r="K52" s="190"/>
+      <c r="L52" s="190"/>
+      <c r="M52" s="190"/>
+      <c r="N52" s="191"/>
+      <c r="O52" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P52" s="145"/>
-      <c r="Q52" s="145"/>
-      <c r="R52" s="145"/>
-      <c r="S52" s="146"/>
-      <c r="T52" s="150" t="s">
+      <c r="P52" s="187"/>
+      <c r="Q52" s="187"/>
+      <c r="R52" s="187"/>
+      <c r="S52" s="188"/>
+      <c r="T52" s="186" t="s">
         <v>153</v>
       </c>
-      <c r="U52" s="145"/>
-      <c r="V52" s="145"/>
-      <c r="W52" s="146"/>
-      <c r="X52" s="150">
+      <c r="U52" s="187"/>
+      <c r="V52" s="187"/>
+      <c r="W52" s="188"/>
+      <c r="X52" s="186">
         <v>1</v>
       </c>
-      <c r="Y52" s="145"/>
-      <c r="Z52" s="146"/>
+      <c r="Y52" s="187"/>
+      <c r="Z52" s="188"/>
     </row>
     <row r="53" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="164"/>
+      <c r="A53" s="196"/>
       <c r="B53" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="C53" s="157" t="s">
+      <c r="C53" s="189" t="s">
         <v>155</v>
       </c>
-      <c r="D53" s="158"/>
-      <c r="E53" s="158"/>
-      <c r="F53" s="158"/>
-      <c r="G53" s="158"/>
-      <c r="H53" s="158"/>
-      <c r="I53" s="158"/>
-      <c r="J53" s="158"/>
-      <c r="K53" s="158"/>
-      <c r="L53" s="158"/>
-      <c r="M53" s="158"/>
-      <c r="N53" s="159"/>
-      <c r="O53" s="150" t="s">
+      <c r="D53" s="190"/>
+      <c r="E53" s="190"/>
+      <c r="F53" s="190"/>
+      <c r="G53" s="190"/>
+      <c r="H53" s="190"/>
+      <c r="I53" s="190"/>
+      <c r="J53" s="190"/>
+      <c r="K53" s="190"/>
+      <c r="L53" s="190"/>
+      <c r="M53" s="190"/>
+      <c r="N53" s="191"/>
+      <c r="O53" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P53" s="145"/>
-      <c r="Q53" s="145"/>
-      <c r="R53" s="145"/>
-      <c r="S53" s="146"/>
-      <c r="T53" s="150" t="s">
+      <c r="P53" s="187"/>
+      <c r="Q53" s="187"/>
+      <c r="R53" s="187"/>
+      <c r="S53" s="188"/>
+      <c r="T53" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="U53" s="145"/>
-      <c r="V53" s="145"/>
-      <c r="W53" s="146"/>
-      <c r="X53" s="150">
+      <c r="U53" s="187"/>
+      <c r="V53" s="187"/>
+      <c r="W53" s="188"/>
+      <c r="X53" s="186">
         <v>1</v>
       </c>
-      <c r="Y53" s="145"/>
-      <c r="Z53" s="146"/>
+      <c r="Y53" s="187"/>
+      <c r="Z53" s="188"/>
     </row>
     <row r="54" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="165" t="s">
+      <c r="A54" s="198" t="s">
         <v>157</v>
       </c>
       <c r="B54" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="C54" s="157" t="s">
+      <c r="C54" s="189" t="s">
         <v>159</v>
       </c>
-      <c r="D54" s="158"/>
-      <c r="E54" s="158"/>
-      <c r="F54" s="158"/>
-      <c r="G54" s="158"/>
-      <c r="H54" s="158"/>
-      <c r="I54" s="158"/>
-      <c r="J54" s="158"/>
-      <c r="K54" s="158"/>
-      <c r="L54" s="158"/>
-      <c r="M54" s="158"/>
-      <c r="N54" s="159"/>
-      <c r="O54" s="150" t="s">
+      <c r="D54" s="190"/>
+      <c r="E54" s="190"/>
+      <c r="F54" s="190"/>
+      <c r="G54" s="190"/>
+      <c r="H54" s="190"/>
+      <c r="I54" s="190"/>
+      <c r="J54" s="190"/>
+      <c r="K54" s="190"/>
+      <c r="L54" s="190"/>
+      <c r="M54" s="190"/>
+      <c r="N54" s="191"/>
+      <c r="O54" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="P54" s="145"/>
-      <c r="Q54" s="145"/>
-      <c r="R54" s="145"/>
-      <c r="S54" s="146"/>
-      <c r="T54" s="150" t="s">
+      <c r="P54" s="187"/>
+      <c r="Q54" s="187"/>
+      <c r="R54" s="187"/>
+      <c r="S54" s="188"/>
+      <c r="T54" s="186" t="s">
         <v>160</v>
       </c>
-      <c r="U54" s="145"/>
-      <c r="V54" s="145"/>
-      <c r="W54" s="146"/>
-      <c r="X54" s="150">
+      <c r="U54" s="187"/>
+      <c r="V54" s="187"/>
+      <c r="W54" s="188"/>
+      <c r="X54" s="186">
         <v>1</v>
       </c>
-      <c r="Y54" s="145"/>
-      <c r="Z54" s="146"/>
+      <c r="Y54" s="187"/>
+      <c r="Z54" s="188"/>
     </row>
     <row r="55" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A55" s="166"/>
+      <c r="A55" s="199"/>
       <c r="B55" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="157" t="s">
+      <c r="C55" s="189" t="s">
         <v>162</v>
       </c>
-      <c r="D55" s="158"/>
-      <c r="E55" s="158"/>
-      <c r="F55" s="158"/>
-      <c r="G55" s="158"/>
-      <c r="H55" s="158"/>
-      <c r="I55" s="158"/>
-      <c r="J55" s="158"/>
-      <c r="K55" s="158"/>
-      <c r="L55" s="158"/>
-      <c r="M55" s="158"/>
-      <c r="N55" s="159"/>
-      <c r="O55" s="150" t="s">
+      <c r="D55" s="190"/>
+      <c r="E55" s="190"/>
+      <c r="F55" s="190"/>
+      <c r="G55" s="190"/>
+      <c r="H55" s="190"/>
+      <c r="I55" s="190"/>
+      <c r="J55" s="190"/>
+      <c r="K55" s="190"/>
+      <c r="L55" s="190"/>
+      <c r="M55" s="190"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P55" s="145"/>
-      <c r="Q55" s="145"/>
-      <c r="R55" s="145"/>
-      <c r="S55" s="146"/>
-      <c r="T55" s="150" t="s">
+      <c r="P55" s="187"/>
+      <c r="Q55" s="187"/>
+      <c r="R55" s="187"/>
+      <c r="S55" s="188"/>
+      <c r="T55" s="186" t="s">
         <v>163</v>
       </c>
-      <c r="U55" s="145"/>
-      <c r="V55" s="145"/>
-      <c r="W55" s="146"/>
-      <c r="X55" s="150">
+      <c r="U55" s="187"/>
+      <c r="V55" s="187"/>
+      <c r="W55" s="188"/>
+      <c r="X55" s="186">
         <v>2</v>
       </c>
-      <c r="Y55" s="145"/>
-      <c r="Z55" s="146"/>
+      <c r="Y55" s="187"/>
+      <c r="Z55" s="188"/>
     </row>
     <row r="56" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A56" s="166"/>
+      <c r="A56" s="199"/>
       <c r="B56" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="157" t="s">
+      <c r="C56" s="189" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="158"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="158"/>
-      <c r="G56" s="158"/>
-      <c r="H56" s="158"/>
-      <c r="I56" s="158"/>
-      <c r="J56" s="158"/>
-      <c r="K56" s="158"/>
-      <c r="L56" s="158"/>
-      <c r="M56" s="158"/>
-      <c r="N56" s="159"/>
-      <c r="O56" s="150" t="s">
+      <c r="D56" s="190"/>
+      <c r="E56" s="190"/>
+      <c r="F56" s="190"/>
+      <c r="G56" s="190"/>
+      <c r="H56" s="190"/>
+      <c r="I56" s="190"/>
+      <c r="J56" s="190"/>
+      <c r="K56" s="190"/>
+      <c r="L56" s="190"/>
+      <c r="M56" s="190"/>
+      <c r="N56" s="191"/>
+      <c r="O56" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P56" s="145"/>
-      <c r="Q56" s="145"/>
-      <c r="R56" s="145"/>
-      <c r="S56" s="146"/>
-      <c r="T56" s="150" t="s">
+      <c r="P56" s="187"/>
+      <c r="Q56" s="187"/>
+      <c r="R56" s="187"/>
+      <c r="S56" s="188"/>
+      <c r="T56" s="186" t="s">
         <v>166</v>
       </c>
-      <c r="U56" s="145"/>
-      <c r="V56" s="145"/>
-      <c r="W56" s="146"/>
-      <c r="X56" s="150">
+      <c r="U56" s="187"/>
+      <c r="V56" s="187"/>
+      <c r="W56" s="188"/>
+      <c r="X56" s="186">
         <v>2</v>
       </c>
-      <c r="Y56" s="145"/>
-      <c r="Z56" s="146"/>
+      <c r="Y56" s="187"/>
+      <c r="Z56" s="188"/>
     </row>
     <row r="57" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A57" s="166"/>
+      <c r="A57" s="199"/>
       <c r="B57" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="157" t="s">
+      <c r="C57" s="189" t="s">
         <v>168</v>
       </c>
-      <c r="D57" s="158"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="158"/>
-      <c r="G57" s="158"/>
-      <c r="H57" s="158"/>
-      <c r="I57" s="158"/>
-      <c r="J57" s="158"/>
-      <c r="K57" s="158"/>
-      <c r="L57" s="158"/>
-      <c r="M57" s="158"/>
-      <c r="N57" s="159"/>
-      <c r="O57" s="150" t="s">
+      <c r="D57" s="190"/>
+      <c r="E57" s="190"/>
+      <c r="F57" s="190"/>
+      <c r="G57" s="190"/>
+      <c r="H57" s="190"/>
+      <c r="I57" s="190"/>
+      <c r="J57" s="190"/>
+      <c r="K57" s="190"/>
+      <c r="L57" s="190"/>
+      <c r="M57" s="190"/>
+      <c r="N57" s="191"/>
+      <c r="O57" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P57" s="145"/>
-      <c r="Q57" s="145"/>
-      <c r="R57" s="145"/>
-      <c r="S57" s="146"/>
-      <c r="T57" s="150" t="s">
+      <c r="P57" s="187"/>
+      <c r="Q57" s="187"/>
+      <c r="R57" s="187"/>
+      <c r="S57" s="188"/>
+      <c r="T57" s="186" t="s">
         <v>169</v>
       </c>
-      <c r="U57" s="145"/>
-      <c r="V57" s="145"/>
-      <c r="W57" s="146"/>
-      <c r="X57" s="150">
+      <c r="U57" s="187"/>
+      <c r="V57" s="187"/>
+      <c r="W57" s="188"/>
+      <c r="X57" s="186">
         <v>2</v>
       </c>
-      <c r="Y57" s="145"/>
-      <c r="Z57" s="146"/>
+      <c r="Y57" s="187"/>
+      <c r="Z57" s="188"/>
     </row>
     <row r="58" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A58" s="167"/>
+      <c r="A58" s="200"/>
       <c r="B58" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="C58" s="157" t="s">
+      <c r="C58" s="189" t="s">
         <v>171</v>
       </c>
-      <c r="D58" s="158"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="158"/>
-      <c r="G58" s="158"/>
-      <c r="H58" s="158"/>
-      <c r="I58" s="158"/>
-      <c r="J58" s="158"/>
-      <c r="K58" s="158"/>
-      <c r="L58" s="158"/>
-      <c r="M58" s="158"/>
-      <c r="N58" s="159"/>
-      <c r="O58" s="150" t="s">
+      <c r="D58" s="190"/>
+      <c r="E58" s="190"/>
+      <c r="F58" s="190"/>
+      <c r="G58" s="190"/>
+      <c r="H58" s="190"/>
+      <c r="I58" s="190"/>
+      <c r="J58" s="190"/>
+      <c r="K58" s="190"/>
+      <c r="L58" s="190"/>
+      <c r="M58" s="190"/>
+      <c r="N58" s="191"/>
+      <c r="O58" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P58" s="145"/>
-      <c r="Q58" s="145"/>
-      <c r="R58" s="145"/>
-      <c r="S58" s="146"/>
-      <c r="T58" s="150" t="s">
+      <c r="P58" s="187"/>
+      <c r="Q58" s="187"/>
+      <c r="R58" s="187"/>
+      <c r="S58" s="188"/>
+      <c r="T58" s="186" t="s">
         <v>172</v>
       </c>
-      <c r="U58" s="145"/>
-      <c r="V58" s="145"/>
-      <c r="W58" s="146"/>
-      <c r="X58" s="150">
+      <c r="U58" s="187"/>
+      <c r="V58" s="187"/>
+      <c r="W58" s="188"/>
+      <c r="X58" s="186">
         <v>22</v>
       </c>
-      <c r="Y58" s="145"/>
-      <c r="Z58" s="146"/>
+      <c r="Y58" s="187"/>
+      <c r="Z58" s="188"/>
     </row>
     <row r="59" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A59" s="66" t="s">
@@ -6560,38 +6560,38 @@
       <c r="B59" s="64" t="s">
         <v>174</v>
       </c>
-      <c r="C59" s="157" t="s">
+      <c r="C59" s="189" t="s">
         <v>175</v>
       </c>
-      <c r="D59" s="158"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
-      <c r="J59" s="158"/>
-      <c r="K59" s="158"/>
-      <c r="L59" s="158"/>
-      <c r="M59" s="158"/>
-      <c r="N59" s="159"/>
-      <c r="O59" s="150" t="s">
+      <c r="D59" s="190"/>
+      <c r="E59" s="190"/>
+      <c r="F59" s="190"/>
+      <c r="G59" s="190"/>
+      <c r="H59" s="190"/>
+      <c r="I59" s="190"/>
+      <c r="J59" s="190"/>
+      <c r="K59" s="190"/>
+      <c r="L59" s="190"/>
+      <c r="M59" s="190"/>
+      <c r="N59" s="191"/>
+      <c r="O59" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P59" s="145"/>
-      <c r="Q59" s="145"/>
-      <c r="R59" s="145"/>
-      <c r="S59" s="146"/>
-      <c r="T59" s="150" t="s">
+      <c r="P59" s="187"/>
+      <c r="Q59" s="187"/>
+      <c r="R59" s="187"/>
+      <c r="S59" s="188"/>
+      <c r="T59" s="186" t="s">
         <v>176</v>
       </c>
-      <c r="U59" s="145"/>
-      <c r="V59" s="145"/>
-      <c r="W59" s="146"/>
-      <c r="X59" s="150">
+      <c r="U59" s="187"/>
+      <c r="V59" s="187"/>
+      <c r="W59" s="188"/>
+      <c r="X59" s="186">
         <v>8</v>
       </c>
-      <c r="Y59" s="145"/>
-      <c r="Z59" s="146"/>
+      <c r="Y59" s="187"/>
+      <c r="Z59" s="188"/>
     </row>
     <row r="60" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A60" s="66" t="s">
@@ -6600,116 +6600,116 @@
       <c r="B60" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="157" t="s">
+      <c r="C60" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="D60" s="158"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="158"/>
-      <c r="H60" s="158"/>
-      <c r="I60" s="158"/>
-      <c r="J60" s="158"/>
-      <c r="K60" s="158"/>
-      <c r="L60" s="158"/>
-      <c r="M60" s="158"/>
-      <c r="N60" s="159"/>
-      <c r="O60" s="150" t="s">
+      <c r="D60" s="190"/>
+      <c r="E60" s="190"/>
+      <c r="F60" s="190"/>
+      <c r="G60" s="190"/>
+      <c r="H60" s="190"/>
+      <c r="I60" s="190"/>
+      <c r="J60" s="190"/>
+      <c r="K60" s="190"/>
+      <c r="L60" s="190"/>
+      <c r="M60" s="190"/>
+      <c r="N60" s="191"/>
+      <c r="O60" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P60" s="145"/>
-      <c r="Q60" s="145"/>
-      <c r="R60" s="145"/>
-      <c r="S60" s="146"/>
-      <c r="T60" s="150" t="s">
+      <c r="P60" s="187"/>
+      <c r="Q60" s="187"/>
+      <c r="R60" s="187"/>
+      <c r="S60" s="188"/>
+      <c r="T60" s="186" t="s">
         <v>179</v>
       </c>
-      <c r="U60" s="145"/>
-      <c r="V60" s="145"/>
-      <c r="W60" s="146"/>
-      <c r="X60" s="150">
+      <c r="U60" s="187"/>
+      <c r="V60" s="187"/>
+      <c r="W60" s="188"/>
+      <c r="X60" s="186">
         <v>1</v>
       </c>
-      <c r="Y60" s="145"/>
-      <c r="Z60" s="146"/>
+      <c r="Y60" s="187"/>
+      <c r="Z60" s="188"/>
     </row>
     <row r="61" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A61" s="160" t="s">
+      <c r="A61" s="201" t="s">
         <v>180</v>
       </c>
       <c r="B61" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="C61" s="157" t="s">
+      <c r="C61" s="189" t="s">
         <v>162</v>
       </c>
-      <c r="D61" s="158"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="158"/>
-      <c r="G61" s="158"/>
-      <c r="H61" s="158"/>
-      <c r="I61" s="158"/>
-      <c r="J61" s="158"/>
-      <c r="K61" s="158"/>
-      <c r="L61" s="158"/>
-      <c r="M61" s="158"/>
-      <c r="N61" s="159"/>
-      <c r="O61" s="150" t="s">
+      <c r="D61" s="190"/>
+      <c r="E61" s="190"/>
+      <c r="F61" s="190"/>
+      <c r="G61" s="190"/>
+      <c r="H61" s="190"/>
+      <c r="I61" s="190"/>
+      <c r="J61" s="190"/>
+      <c r="K61" s="190"/>
+      <c r="L61" s="190"/>
+      <c r="M61" s="190"/>
+      <c r="N61" s="191"/>
+      <c r="O61" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P61" s="145"/>
-      <c r="Q61" s="145"/>
-      <c r="R61" s="145"/>
-      <c r="S61" s="146"/>
-      <c r="T61" s="150" t="s">
+      <c r="P61" s="187"/>
+      <c r="Q61" s="187"/>
+      <c r="R61" s="187"/>
+      <c r="S61" s="188"/>
+      <c r="T61" s="186" t="s">
         <v>163</v>
       </c>
-      <c r="U61" s="145"/>
-      <c r="V61" s="145"/>
-      <c r="W61" s="146"/>
-      <c r="X61" s="150">
+      <c r="U61" s="187"/>
+      <c r="V61" s="187"/>
+      <c r="W61" s="188"/>
+      <c r="X61" s="186">
         <v>2</v>
       </c>
-      <c r="Y61" s="145"/>
-      <c r="Z61" s="146"/>
+      <c r="Y61" s="187"/>
+      <c r="Z61" s="188"/>
     </row>
     <row r="62" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A62" s="161"/>
+      <c r="A62" s="202"/>
       <c r="B62" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="157" t="s">
+      <c r="C62" s="189" t="s">
         <v>183</v>
       </c>
-      <c r="D62" s="158"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="158"/>
-      <c r="G62" s="158"/>
-      <c r="H62" s="158"/>
-      <c r="I62" s="158"/>
-      <c r="J62" s="158"/>
-      <c r="K62" s="158"/>
-      <c r="L62" s="158"/>
-      <c r="M62" s="158"/>
-      <c r="N62" s="159"/>
-      <c r="O62" s="150" t="s">
+      <c r="D62" s="190"/>
+      <c r="E62" s="190"/>
+      <c r="F62" s="190"/>
+      <c r="G62" s="190"/>
+      <c r="H62" s="190"/>
+      <c r="I62" s="190"/>
+      <c r="J62" s="190"/>
+      <c r="K62" s="190"/>
+      <c r="L62" s="190"/>
+      <c r="M62" s="190"/>
+      <c r="N62" s="191"/>
+      <c r="O62" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="P62" s="145"/>
-      <c r="Q62" s="145"/>
-      <c r="R62" s="145"/>
-      <c r="S62" s="146"/>
-      <c r="T62" s="150" t="s">
+      <c r="P62" s="187"/>
+      <c r="Q62" s="187"/>
+      <c r="R62" s="187"/>
+      <c r="S62" s="188"/>
+      <c r="T62" s="186" t="s">
         <v>184</v>
       </c>
-      <c r="U62" s="145"/>
-      <c r="V62" s="145"/>
-      <c r="W62" s="146"/>
-      <c r="X62" s="150">
+      <c r="U62" s="187"/>
+      <c r="V62" s="187"/>
+      <c r="W62" s="188"/>
+      <c r="X62" s="186">
         <v>1</v>
       </c>
-      <c r="Y62" s="145"/>
-      <c r="Z62" s="146"/>
+      <c r="Y62" s="187"/>
+      <c r="Z62" s="188"/>
     </row>
     <row r="63" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A63" s="66" t="s">
@@ -6718,38 +6718,38 @@
       <c r="B63" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C63" s="157" t="s">
+      <c r="C63" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="158"/>
-      <c r="E63" s="158"/>
-      <c r="F63" s="158"/>
-      <c r="G63" s="158"/>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158"/>
-      <c r="J63" s="158"/>
-      <c r="K63" s="158"/>
-      <c r="L63" s="158"/>
-      <c r="M63" s="158"/>
-      <c r="N63" s="159"/>
-      <c r="O63" s="150" t="s">
+      <c r="D63" s="190"/>
+      <c r="E63" s="190"/>
+      <c r="F63" s="190"/>
+      <c r="G63" s="190"/>
+      <c r="H63" s="190"/>
+      <c r="I63" s="190"/>
+      <c r="J63" s="190"/>
+      <c r="K63" s="190"/>
+      <c r="L63" s="190"/>
+      <c r="M63" s="190"/>
+      <c r="N63" s="191"/>
+      <c r="O63" s="186" t="s">
         <v>133</v>
       </c>
-      <c r="P63" s="145"/>
-      <c r="Q63" s="145"/>
-      <c r="R63" s="145"/>
-      <c r="S63" s="146"/>
-      <c r="T63" s="150" t="s">
+      <c r="P63" s="187"/>
+      <c r="Q63" s="187"/>
+      <c r="R63" s="187"/>
+      <c r="S63" s="188"/>
+      <c r="T63" s="186" t="s">
         <v>137</v>
       </c>
-      <c r="U63" s="145"/>
-      <c r="V63" s="145"/>
-      <c r="W63" s="146"/>
-      <c r="X63" s="150">
+      <c r="U63" s="187"/>
+      <c r="V63" s="187"/>
+      <c r="W63" s="188"/>
+      <c r="X63" s="186">
         <v>1</v>
       </c>
-      <c r="Y63" s="145"/>
-      <c r="Z63" s="146"/>
+      <c r="Y63" s="187"/>
+      <c r="Z63" s="188"/>
     </row>
     <row r="64" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A64" s="66" t="s">
@@ -6758,38 +6758,38 @@
       <c r="B64" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="C64" s="157" t="s">
+      <c r="C64" s="189" t="s">
         <v>159</v>
       </c>
-      <c r="D64" s="158"/>
-      <c r="E64" s="158"/>
-      <c r="F64" s="158"/>
-      <c r="G64" s="158"/>
-      <c r="H64" s="158"/>
-      <c r="I64" s="158"/>
-      <c r="J64" s="158"/>
-      <c r="K64" s="158"/>
-      <c r="L64" s="158"/>
-      <c r="M64" s="158"/>
-      <c r="N64" s="159"/>
-      <c r="O64" s="150" t="s">
+      <c r="D64" s="190"/>
+      <c r="E64" s="190"/>
+      <c r="F64" s="190"/>
+      <c r="G64" s="190"/>
+      <c r="H64" s="190"/>
+      <c r="I64" s="190"/>
+      <c r="J64" s="190"/>
+      <c r="K64" s="190"/>
+      <c r="L64" s="190"/>
+      <c r="M64" s="190"/>
+      <c r="N64" s="191"/>
+      <c r="O64" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="P64" s="145"/>
-      <c r="Q64" s="145"/>
-      <c r="R64" s="145"/>
-      <c r="S64" s="146"/>
-      <c r="T64" s="150" t="s">
+      <c r="P64" s="187"/>
+      <c r="Q64" s="187"/>
+      <c r="R64" s="187"/>
+      <c r="S64" s="188"/>
+      <c r="T64" s="186" t="s">
         <v>160</v>
       </c>
-      <c r="U64" s="145"/>
-      <c r="V64" s="145"/>
-      <c r="W64" s="146"/>
-      <c r="X64" s="150">
+      <c r="U64" s="187"/>
+      <c r="V64" s="187"/>
+      <c r="W64" s="188"/>
+      <c r="X64" s="186">
         <v>1</v>
       </c>
-      <c r="Y64" s="145"/>
-      <c r="Z64" s="146"/>
+      <c r="Y64" s="187"/>
+      <c r="Z64" s="188"/>
     </row>
     <row r="65" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A65" s="66" t="s">
@@ -6798,38 +6798,38 @@
       <c r="B65" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="C65" s="157" t="s">
+      <c r="C65" s="189" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="158"/>
-      <c r="E65" s="158"/>
-      <c r="F65" s="158"/>
-      <c r="G65" s="158"/>
-      <c r="H65" s="158"/>
-      <c r="I65" s="158"/>
-      <c r="J65" s="158"/>
-      <c r="K65" s="158"/>
-      <c r="L65" s="158"/>
-      <c r="M65" s="158"/>
-      <c r="N65" s="159"/>
-      <c r="O65" s="150" t="s">
+      <c r="D65" s="190"/>
+      <c r="E65" s="190"/>
+      <c r="F65" s="190"/>
+      <c r="G65" s="190"/>
+      <c r="H65" s="190"/>
+      <c r="I65" s="190"/>
+      <c r="J65" s="190"/>
+      <c r="K65" s="190"/>
+      <c r="L65" s="190"/>
+      <c r="M65" s="190"/>
+      <c r="N65" s="191"/>
+      <c r="O65" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P65" s="145"/>
-      <c r="Q65" s="145"/>
-      <c r="R65" s="145"/>
-      <c r="S65" s="146"/>
-      <c r="T65" s="150" t="s">
+      <c r="P65" s="187"/>
+      <c r="Q65" s="187"/>
+      <c r="R65" s="187"/>
+      <c r="S65" s="188"/>
+      <c r="T65" s="186" t="s">
         <v>191</v>
       </c>
-      <c r="U65" s="145"/>
-      <c r="V65" s="145"/>
-      <c r="W65" s="146"/>
-      <c r="X65" s="150">
+      <c r="U65" s="187"/>
+      <c r="V65" s="187"/>
+      <c r="W65" s="188"/>
+      <c r="X65" s="186">
         <v>1</v>
       </c>
-      <c r="Y65" s="145"/>
-      <c r="Z65" s="146"/>
+      <c r="Y65" s="187"/>
+      <c r="Z65" s="188"/>
     </row>
     <row r="66" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A66" s="66" t="s">
@@ -6838,38 +6838,38 @@
       <c r="B66" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="C66" s="157" t="s">
+      <c r="C66" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="D66" s="158"/>
-      <c r="E66" s="158"/>
-      <c r="F66" s="158"/>
-      <c r="G66" s="158"/>
-      <c r="H66" s="158"/>
-      <c r="I66" s="158"/>
-      <c r="J66" s="158"/>
-      <c r="K66" s="158"/>
-      <c r="L66" s="158"/>
-      <c r="M66" s="158"/>
-      <c r="N66" s="159"/>
-      <c r="O66" s="150" t="s">
+      <c r="D66" s="190"/>
+      <c r="E66" s="190"/>
+      <c r="F66" s="190"/>
+      <c r="G66" s="190"/>
+      <c r="H66" s="190"/>
+      <c r="I66" s="190"/>
+      <c r="J66" s="190"/>
+      <c r="K66" s="190"/>
+      <c r="L66" s="190"/>
+      <c r="M66" s="190"/>
+      <c r="N66" s="191"/>
+      <c r="O66" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="P66" s="145"/>
-      <c r="Q66" s="145"/>
-      <c r="R66" s="145"/>
-      <c r="S66" s="146"/>
-      <c r="T66" s="150" t="s">
+      <c r="P66" s="187"/>
+      <c r="Q66" s="187"/>
+      <c r="R66" s="187"/>
+      <c r="S66" s="188"/>
+      <c r="T66" s="186" t="s">
         <v>153</v>
       </c>
-      <c r="U66" s="145"/>
-      <c r="V66" s="145"/>
-      <c r="W66" s="146"/>
-      <c r="X66" s="150">
+      <c r="U66" s="187"/>
+      <c r="V66" s="187"/>
+      <c r="W66" s="188"/>
+      <c r="X66" s="186">
         <v>1</v>
       </c>
-      <c r="Y66" s="145"/>
-      <c r="Z66" s="146"/>
+      <c r="Y66" s="187"/>
+      <c r="Z66" s="188"/>
     </row>
     <row r="67" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A67" s="66" t="s">
@@ -6878,38 +6878,38 @@
       <c r="B67" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="157" t="s">
+      <c r="C67" s="189" t="s">
         <v>196</v>
       </c>
-      <c r="D67" s="158"/>
-      <c r="E67" s="158"/>
-      <c r="F67" s="158"/>
-      <c r="G67" s="158"/>
-      <c r="H67" s="158"/>
-      <c r="I67" s="158"/>
-      <c r="J67" s="158"/>
-      <c r="K67" s="158"/>
-      <c r="L67" s="158"/>
-      <c r="M67" s="158"/>
-      <c r="N67" s="159"/>
-      <c r="O67" s="150" t="s">
+      <c r="D67" s="190"/>
+      <c r="E67" s="190"/>
+      <c r="F67" s="190"/>
+      <c r="G67" s="190"/>
+      <c r="H67" s="190"/>
+      <c r="I67" s="190"/>
+      <c r="J67" s="190"/>
+      <c r="K67" s="190"/>
+      <c r="L67" s="190"/>
+      <c r="M67" s="190"/>
+      <c r="N67" s="191"/>
+      <c r="O67" s="186" t="s">
         <v>133</v>
       </c>
-      <c r="P67" s="145"/>
-      <c r="Q67" s="145"/>
-      <c r="R67" s="145"/>
-      <c r="S67" s="146"/>
-      <c r="T67" s="150" t="s">
+      <c r="P67" s="187"/>
+      <c r="Q67" s="187"/>
+      <c r="R67" s="187"/>
+      <c r="S67" s="188"/>
+      <c r="T67" s="186" t="s">
         <v>134</v>
       </c>
-      <c r="U67" s="145"/>
-      <c r="V67" s="145"/>
-      <c r="W67" s="146"/>
-      <c r="X67" s="150">
+      <c r="U67" s="187"/>
+      <c r="V67" s="187"/>
+      <c r="W67" s="188"/>
+      <c r="X67" s="186">
         <v>6</v>
       </c>
-      <c r="Y67" s="145"/>
-      <c r="Z67" s="146"/>
+      <c r="Y67" s="187"/>
+      <c r="Z67" s="188"/>
     </row>
     <row r="68" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A68" s="64">
@@ -6918,38 +6918,38 @@
       <c r="B68" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="C68" s="144" t="s">
+      <c r="C68" s="203" t="s">
         <v>198</v>
       </c>
-      <c r="D68" s="155"/>
-      <c r="E68" s="155"/>
-      <c r="F68" s="155"/>
-      <c r="G68" s="155"/>
-      <c r="H68" s="155"/>
-      <c r="I68" s="155"/>
-      <c r="J68" s="155"/>
-      <c r="K68" s="155"/>
-      <c r="L68" s="155"/>
-      <c r="M68" s="155"/>
-      <c r="N68" s="156"/>
-      <c r="O68" s="147" t="s">
+      <c r="D68" s="204"/>
+      <c r="E68" s="204"/>
+      <c r="F68" s="204"/>
+      <c r="G68" s="204"/>
+      <c r="H68" s="204"/>
+      <c r="I68" s="204"/>
+      <c r="J68" s="204"/>
+      <c r="K68" s="204"/>
+      <c r="L68" s="204"/>
+      <c r="M68" s="204"/>
+      <c r="N68" s="205"/>
+      <c r="O68" s="206" t="s">
         <v>122</v>
       </c>
-      <c r="P68" s="148"/>
-      <c r="Q68" s="148"/>
-      <c r="R68" s="148"/>
-      <c r="S68" s="149"/>
-      <c r="T68" s="150" t="s">
+      <c r="P68" s="207"/>
+      <c r="Q68" s="207"/>
+      <c r="R68" s="207"/>
+      <c r="S68" s="208"/>
+      <c r="T68" s="186" t="s">
         <v>123</v>
       </c>
-      <c r="U68" s="145"/>
-      <c r="V68" s="145"/>
-      <c r="W68" s="146"/>
-      <c r="X68" s="150">
+      <c r="U68" s="187"/>
+      <c r="V68" s="187"/>
+      <c r="W68" s="188"/>
+      <c r="X68" s="186">
         <v>1</v>
       </c>
-      <c r="Y68" s="145"/>
-      <c r="Z68" s="146"/>
+      <c r="Y68" s="187"/>
+      <c r="Z68" s="188"/>
     </row>
     <row r="69" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A69" s="64" t="s">
@@ -6958,38 +6958,38 @@
       <c r="B69" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="C69" s="144" t="s">
+      <c r="C69" s="203" t="s">
         <v>200</v>
       </c>
-      <c r="D69" s="155"/>
-      <c r="E69" s="155"/>
-      <c r="F69" s="155"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="155"/>
-      <c r="I69" s="155"/>
-      <c r="J69" s="155"/>
-      <c r="K69" s="155"/>
-      <c r="L69" s="155"/>
-      <c r="M69" s="155"/>
-      <c r="N69" s="156"/>
-      <c r="O69" s="147" t="s">
+      <c r="D69" s="204"/>
+      <c r="E69" s="204"/>
+      <c r="F69" s="204"/>
+      <c r="G69" s="204"/>
+      <c r="H69" s="204"/>
+      <c r="I69" s="204"/>
+      <c r="J69" s="204"/>
+      <c r="K69" s="204"/>
+      <c r="L69" s="204"/>
+      <c r="M69" s="204"/>
+      <c r="N69" s="205"/>
+      <c r="O69" s="206" t="s">
         <v>122</v>
       </c>
-      <c r="P69" s="148"/>
-      <c r="Q69" s="148"/>
-      <c r="R69" s="148"/>
-      <c r="S69" s="149"/>
-      <c r="T69" s="150" t="s">
+      <c r="P69" s="207"/>
+      <c r="Q69" s="207"/>
+      <c r="R69" s="207"/>
+      <c r="S69" s="208"/>
+      <c r="T69" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="U69" s="145"/>
-      <c r="V69" s="145"/>
-      <c r="W69" s="146"/>
-      <c r="X69" s="150">
+      <c r="U69" s="187"/>
+      <c r="V69" s="187"/>
+      <c r="W69" s="188"/>
+      <c r="X69" s="186">
         <v>1</v>
       </c>
-      <c r="Y69" s="145"/>
-      <c r="Z69" s="146"/>
+      <c r="Y69" s="187"/>
+      <c r="Z69" s="188"/>
     </row>
     <row r="70" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A70" s="64" t="s">
@@ -6998,38 +6998,38 @@
       <c r="B70" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="144" t="s">
+      <c r="C70" s="203" t="s">
         <v>202</v>
       </c>
-      <c r="D70" s="155"/>
-      <c r="E70" s="155"/>
-      <c r="F70" s="155"/>
-      <c r="G70" s="155"/>
-      <c r="H70" s="155"/>
-      <c r="I70" s="155"/>
-      <c r="J70" s="155"/>
-      <c r="K70" s="155"/>
-      <c r="L70" s="155"/>
-      <c r="M70" s="155"/>
-      <c r="N70" s="156"/>
-      <c r="O70" s="147" t="s">
+      <c r="D70" s="204"/>
+      <c r="E70" s="204"/>
+      <c r="F70" s="204"/>
+      <c r="G70" s="204"/>
+      <c r="H70" s="204"/>
+      <c r="I70" s="204"/>
+      <c r="J70" s="204"/>
+      <c r="K70" s="204"/>
+      <c r="L70" s="204"/>
+      <c r="M70" s="204"/>
+      <c r="N70" s="205"/>
+      <c r="O70" s="206" t="s">
         <v>129</v>
       </c>
-      <c r="P70" s="148"/>
-      <c r="Q70" s="148"/>
-      <c r="R70" s="148"/>
-      <c r="S70" s="149"/>
-      <c r="T70" s="150" t="s">
+      <c r="P70" s="207"/>
+      <c r="Q70" s="207"/>
+      <c r="R70" s="207"/>
+      <c r="S70" s="208"/>
+      <c r="T70" s="186" t="s">
         <v>130</v>
       </c>
-      <c r="U70" s="145"/>
-      <c r="V70" s="145"/>
-      <c r="W70" s="146"/>
-      <c r="X70" s="150">
+      <c r="U70" s="187"/>
+      <c r="V70" s="187"/>
+      <c r="W70" s="188"/>
+      <c r="X70" s="186">
         <v>6</v>
       </c>
-      <c r="Y70" s="145"/>
-      <c r="Z70" s="146"/>
+      <c r="Y70" s="187"/>
+      <c r="Z70" s="188"/>
     </row>
     <row r="71" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A71" s="64" t="s">
@@ -7038,38 +7038,38 @@
       <c r="B71" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="144" t="s">
+      <c r="C71" s="203" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="155"/>
-      <c r="E71" s="155"/>
-      <c r="F71" s="155"/>
-      <c r="G71" s="155"/>
-      <c r="H71" s="155"/>
-      <c r="I71" s="155"/>
-      <c r="J71" s="155"/>
-      <c r="K71" s="155"/>
-      <c r="L71" s="155"/>
-      <c r="M71" s="155"/>
-      <c r="N71" s="156"/>
-      <c r="O71" s="147" t="s">
+      <c r="D71" s="204"/>
+      <c r="E71" s="204"/>
+      <c r="F71" s="204"/>
+      <c r="G71" s="204"/>
+      <c r="H71" s="204"/>
+      <c r="I71" s="204"/>
+      <c r="J71" s="204"/>
+      <c r="K71" s="204"/>
+      <c r="L71" s="204"/>
+      <c r="M71" s="204"/>
+      <c r="N71" s="205"/>
+      <c r="O71" s="206" t="s">
         <v>133</v>
       </c>
-      <c r="P71" s="148"/>
-      <c r="Q71" s="148"/>
-      <c r="R71" s="148"/>
-      <c r="S71" s="149"/>
-      <c r="T71" s="150" t="s">
+      <c r="P71" s="207"/>
+      <c r="Q71" s="207"/>
+      <c r="R71" s="207"/>
+      <c r="S71" s="208"/>
+      <c r="T71" s="186" t="s">
         <v>134</v>
       </c>
-      <c r="U71" s="145"/>
-      <c r="V71" s="145"/>
-      <c r="W71" s="146"/>
-      <c r="X71" s="150">
+      <c r="U71" s="187"/>
+      <c r="V71" s="187"/>
+      <c r="W71" s="188"/>
+      <c r="X71" s="186">
         <v>6</v>
       </c>
-      <c r="Y71" s="145"/>
-      <c r="Z71" s="146"/>
+      <c r="Y71" s="187"/>
+      <c r="Z71" s="188"/>
     </row>
     <row r="72" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A72" s="64" t="s">
@@ -7078,38 +7078,38 @@
       <c r="B72" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="144" t="s">
+      <c r="C72" s="203" t="s">
         <v>206</v>
       </c>
-      <c r="D72" s="155"/>
-      <c r="E72" s="155"/>
-      <c r="F72" s="155"/>
-      <c r="G72" s="155"/>
-      <c r="H72" s="155"/>
-      <c r="I72" s="155"/>
-      <c r="J72" s="155"/>
-      <c r="K72" s="155"/>
-      <c r="L72" s="155"/>
-      <c r="M72" s="155"/>
-      <c r="N72" s="156"/>
-      <c r="O72" s="147" t="s">
+      <c r="D72" s="204"/>
+      <c r="E72" s="204"/>
+      <c r="F72" s="204"/>
+      <c r="G72" s="204"/>
+      <c r="H72" s="204"/>
+      <c r="I72" s="204"/>
+      <c r="J72" s="204"/>
+      <c r="K72" s="204"/>
+      <c r="L72" s="204"/>
+      <c r="M72" s="204"/>
+      <c r="N72" s="205"/>
+      <c r="O72" s="206" t="s">
         <v>133</v>
       </c>
-      <c r="P72" s="148"/>
-      <c r="Q72" s="148"/>
-      <c r="R72" s="148"/>
-      <c r="S72" s="149"/>
-      <c r="T72" s="150" t="s">
+      <c r="P72" s="207"/>
+      <c r="Q72" s="207"/>
+      <c r="R72" s="207"/>
+      <c r="S72" s="208"/>
+      <c r="T72" s="186" t="s">
         <v>137</v>
       </c>
-      <c r="U72" s="145"/>
-      <c r="V72" s="145"/>
-      <c r="W72" s="146"/>
-      <c r="X72" s="150">
+      <c r="U72" s="187"/>
+      <c r="V72" s="187"/>
+      <c r="W72" s="188"/>
+      <c r="X72" s="186">
         <v>6</v>
       </c>
-      <c r="Y72" s="145"/>
-      <c r="Z72" s="146"/>
+      <c r="Y72" s="187"/>
+      <c r="Z72" s="188"/>
     </row>
     <row r="73" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A73" s="64">
@@ -7118,38 +7118,38 @@
       <c r="B73" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C73" s="144" t="s">
+      <c r="C73" s="203" t="s">
         <v>208</v>
       </c>
-      <c r="D73" s="145"/>
-      <c r="E73" s="145"/>
-      <c r="F73" s="145"/>
-      <c r="G73" s="145"/>
-      <c r="H73" s="145"/>
-      <c r="I73" s="145"/>
-      <c r="J73" s="145"/>
-      <c r="K73" s="145"/>
-      <c r="L73" s="145"/>
-      <c r="M73" s="145"/>
-      <c r="N73" s="146"/>
-      <c r="O73" s="147" t="s">
+      <c r="D73" s="187"/>
+      <c r="E73" s="187"/>
+      <c r="F73" s="187"/>
+      <c r="G73" s="187"/>
+      <c r="H73" s="187"/>
+      <c r="I73" s="187"/>
+      <c r="J73" s="187"/>
+      <c r="K73" s="187"/>
+      <c r="L73" s="187"/>
+      <c r="M73" s="187"/>
+      <c r="N73" s="188"/>
+      <c r="O73" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P73" s="148"/>
-      <c r="Q73" s="148"/>
-      <c r="R73" s="148"/>
-      <c r="S73" s="149"/>
-      <c r="T73" s="150" t="s">
+      <c r="P73" s="207"/>
+      <c r="Q73" s="207"/>
+      <c r="R73" s="207"/>
+      <c r="S73" s="208"/>
+      <c r="T73" s="186" t="s">
         <v>147</v>
       </c>
-      <c r="U73" s="145"/>
-      <c r="V73" s="145"/>
-      <c r="W73" s="146"/>
-      <c r="X73" s="152">
+      <c r="U73" s="187"/>
+      <c r="V73" s="187"/>
+      <c r="W73" s="188"/>
+      <c r="X73" s="209">
         <v>1</v>
       </c>
-      <c r="Y73" s="153"/>
-      <c r="Z73" s="154"/>
+      <c r="Y73" s="210"/>
+      <c r="Z73" s="211"/>
     </row>
     <row r="74" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A74" s="64" t="s">
@@ -7158,38 +7158,38 @@
       <c r="B74" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="203" t="s">
         <v>210</v>
       </c>
-      <c r="D74" s="145"/>
-      <c r="E74" s="145"/>
-      <c r="F74" s="145"/>
-      <c r="G74" s="145"/>
-      <c r="H74" s="145"/>
-      <c r="I74" s="145"/>
-      <c r="J74" s="145"/>
-      <c r="K74" s="145"/>
-      <c r="L74" s="145"/>
-      <c r="M74" s="145"/>
-      <c r="N74" s="146"/>
-      <c r="O74" s="147" t="s">
+      <c r="D74" s="187"/>
+      <c r="E74" s="187"/>
+      <c r="F74" s="187"/>
+      <c r="G74" s="187"/>
+      <c r="H74" s="187"/>
+      <c r="I74" s="187"/>
+      <c r="J74" s="187"/>
+      <c r="K74" s="187"/>
+      <c r="L74" s="187"/>
+      <c r="M74" s="187"/>
+      <c r="N74" s="188"/>
+      <c r="O74" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P74" s="148"/>
-      <c r="Q74" s="148"/>
-      <c r="R74" s="148"/>
-      <c r="S74" s="149"/>
-      <c r="T74" s="150" t="s">
+      <c r="P74" s="207"/>
+      <c r="Q74" s="207"/>
+      <c r="R74" s="207"/>
+      <c r="S74" s="208"/>
+      <c r="T74" s="186" t="s">
         <v>150</v>
       </c>
-      <c r="U74" s="145"/>
-      <c r="V74" s="145"/>
-      <c r="W74" s="146"/>
-      <c r="X74" s="152">
+      <c r="U74" s="187"/>
+      <c r="V74" s="187"/>
+      <c r="W74" s="188"/>
+      <c r="X74" s="209">
         <v>4</v>
       </c>
-      <c r="Y74" s="153"/>
-      <c r="Z74" s="154"/>
+      <c r="Y74" s="210"/>
+      <c r="Z74" s="211"/>
     </row>
     <row r="75" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A75" s="64" t="s">
@@ -7198,38 +7198,38 @@
       <c r="B75" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C75" s="144" t="s">
+      <c r="C75" s="203" t="s">
         <v>212</v>
       </c>
-      <c r="D75" s="145"/>
-      <c r="E75" s="145"/>
-      <c r="F75" s="145"/>
-      <c r="G75" s="145"/>
-      <c r="H75" s="145"/>
-      <c r="I75" s="145"/>
-      <c r="J75" s="145"/>
-      <c r="K75" s="145"/>
-      <c r="L75" s="145"/>
-      <c r="M75" s="145"/>
-      <c r="N75" s="146"/>
-      <c r="O75" s="147" t="s">
+      <c r="D75" s="187"/>
+      <c r="E75" s="187"/>
+      <c r="F75" s="187"/>
+      <c r="G75" s="187"/>
+      <c r="H75" s="187"/>
+      <c r="I75" s="187"/>
+      <c r="J75" s="187"/>
+      <c r="K75" s="187"/>
+      <c r="L75" s="187"/>
+      <c r="M75" s="187"/>
+      <c r="N75" s="188"/>
+      <c r="O75" s="206" t="s">
         <v>122</v>
       </c>
-      <c r="P75" s="148"/>
-      <c r="Q75" s="148"/>
-      <c r="R75" s="148"/>
-      <c r="S75" s="149"/>
-      <c r="T75" s="150" t="s">
+      <c r="P75" s="207"/>
+      <c r="Q75" s="207"/>
+      <c r="R75" s="207"/>
+      <c r="S75" s="208"/>
+      <c r="T75" s="186" t="s">
         <v>153</v>
       </c>
-      <c r="U75" s="145"/>
-      <c r="V75" s="145"/>
-      <c r="W75" s="146"/>
-      <c r="X75" s="152">
+      <c r="U75" s="187"/>
+      <c r="V75" s="187"/>
+      <c r="W75" s="188"/>
+      <c r="X75" s="209">
         <v>1</v>
       </c>
-      <c r="Y75" s="153"/>
-      <c r="Z75" s="154"/>
+      <c r="Y75" s="210"/>
+      <c r="Z75" s="211"/>
     </row>
     <row r="76" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A76" s="64" t="s">
@@ -7238,38 +7238,38 @@
       <c r="B76" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C76" s="144" t="s">
+      <c r="C76" s="203" t="s">
         <v>214</v>
       </c>
-      <c r="D76" s="145"/>
-      <c r="E76" s="145"/>
-      <c r="F76" s="145"/>
-      <c r="G76" s="145"/>
-      <c r="H76" s="145"/>
-      <c r="I76" s="145"/>
-      <c r="J76" s="145"/>
-      <c r="K76" s="145"/>
-      <c r="L76" s="145"/>
-      <c r="M76" s="145"/>
-      <c r="N76" s="146"/>
-      <c r="O76" s="147" t="s">
+      <c r="D76" s="187"/>
+      <c r="E76" s="187"/>
+      <c r="F76" s="187"/>
+      <c r="G76" s="187"/>
+      <c r="H76" s="187"/>
+      <c r="I76" s="187"/>
+      <c r="J76" s="187"/>
+      <c r="K76" s="187"/>
+      <c r="L76" s="187"/>
+      <c r="M76" s="187"/>
+      <c r="N76" s="188"/>
+      <c r="O76" s="206" t="s">
         <v>122</v>
       </c>
-      <c r="P76" s="148"/>
-      <c r="Q76" s="148"/>
-      <c r="R76" s="148"/>
-      <c r="S76" s="149"/>
-      <c r="T76" s="150" t="s">
+      <c r="P76" s="207"/>
+      <c r="Q76" s="207"/>
+      <c r="R76" s="207"/>
+      <c r="S76" s="208"/>
+      <c r="T76" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="U76" s="145"/>
-      <c r="V76" s="145"/>
-      <c r="W76" s="146"/>
-      <c r="X76" s="152">
+      <c r="U76" s="187"/>
+      <c r="V76" s="187"/>
+      <c r="W76" s="188"/>
+      <c r="X76" s="209">
         <v>1</v>
       </c>
-      <c r="Y76" s="153"/>
-      <c r="Z76" s="154"/>
+      <c r="Y76" s="210"/>
+      <c r="Z76" s="211"/>
     </row>
     <row r="77" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A77" s="64">
@@ -7278,38 +7278,38 @@
       <c r="B77" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="C77" s="144" t="s">
+      <c r="C77" s="203" t="s">
         <v>216</v>
       </c>
-      <c r="D77" s="145"/>
-      <c r="E77" s="145"/>
-      <c r="F77" s="145"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="145"/>
-      <c r="I77" s="145"/>
-      <c r="J77" s="145"/>
-      <c r="K77" s="145"/>
-      <c r="L77" s="145"/>
-      <c r="M77" s="145"/>
-      <c r="N77" s="146"/>
-      <c r="O77" s="150" t="s">
+      <c r="D77" s="187"/>
+      <c r="E77" s="187"/>
+      <c r="F77" s="187"/>
+      <c r="G77" s="187"/>
+      <c r="H77" s="187"/>
+      <c r="I77" s="187"/>
+      <c r="J77" s="187"/>
+      <c r="K77" s="187"/>
+      <c r="L77" s="187"/>
+      <c r="M77" s="187"/>
+      <c r="N77" s="188"/>
+      <c r="O77" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="P77" s="145"/>
-      <c r="Q77" s="145"/>
-      <c r="R77" s="145"/>
-      <c r="S77" s="146"/>
-      <c r="T77" s="150" t="s">
+      <c r="P77" s="187"/>
+      <c r="Q77" s="187"/>
+      <c r="R77" s="187"/>
+      <c r="S77" s="188"/>
+      <c r="T77" s="186" t="s">
         <v>160</v>
       </c>
-      <c r="U77" s="145"/>
-      <c r="V77" s="145"/>
-      <c r="W77" s="146"/>
-      <c r="X77" s="150">
+      <c r="U77" s="187"/>
+      <c r="V77" s="187"/>
+      <c r="W77" s="188"/>
+      <c r="X77" s="186">
         <v>1</v>
       </c>
-      <c r="Y77" s="145"/>
-      <c r="Z77" s="146"/>
+      <c r="Y77" s="187"/>
+      <c r="Z77" s="188"/>
     </row>
     <row r="78" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A78" s="64" t="s">
@@ -7318,38 +7318,38 @@
       <c r="B78" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="203" t="s">
         <v>218</v>
       </c>
-      <c r="D78" s="145"/>
-      <c r="E78" s="145"/>
-      <c r="F78" s="145"/>
-      <c r="G78" s="145"/>
-      <c r="H78" s="145"/>
-      <c r="I78" s="145"/>
-      <c r="J78" s="145"/>
-      <c r="K78" s="145"/>
-      <c r="L78" s="145"/>
-      <c r="M78" s="145"/>
-      <c r="N78" s="146"/>
-      <c r="O78" s="147" t="s">
+      <c r="D78" s="187"/>
+      <c r="E78" s="187"/>
+      <c r="F78" s="187"/>
+      <c r="G78" s="187"/>
+      <c r="H78" s="187"/>
+      <c r="I78" s="187"/>
+      <c r="J78" s="187"/>
+      <c r="K78" s="187"/>
+      <c r="L78" s="187"/>
+      <c r="M78" s="187"/>
+      <c r="N78" s="188"/>
+      <c r="O78" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P78" s="148"/>
-      <c r="Q78" s="148"/>
-      <c r="R78" s="148"/>
-      <c r="S78" s="149"/>
-      <c r="T78" s="150" t="s">
+      <c r="P78" s="207"/>
+      <c r="Q78" s="207"/>
+      <c r="R78" s="207"/>
+      <c r="S78" s="208"/>
+      <c r="T78" s="186" t="s">
         <v>163</v>
       </c>
-      <c r="U78" s="145"/>
-      <c r="V78" s="145"/>
-      <c r="W78" s="146"/>
-      <c r="X78" s="150">
+      <c r="U78" s="187"/>
+      <c r="V78" s="187"/>
+      <c r="W78" s="188"/>
+      <c r="X78" s="186">
         <v>2</v>
       </c>
-      <c r="Y78" s="145"/>
-      <c r="Z78" s="146"/>
+      <c r="Y78" s="187"/>
+      <c r="Z78" s="188"/>
     </row>
     <row r="79" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A79" s="64" t="s">
@@ -7358,38 +7358,38 @@
       <c r="B79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="C79" s="144" t="s">
+      <c r="C79" s="203" t="s">
         <v>220</v>
       </c>
-      <c r="D79" s="145"/>
-      <c r="E79" s="145"/>
-      <c r="F79" s="145"/>
-      <c r="G79" s="145"/>
-      <c r="H79" s="145"/>
-      <c r="I79" s="145"/>
-      <c r="J79" s="145"/>
-      <c r="K79" s="145"/>
-      <c r="L79" s="145"/>
-      <c r="M79" s="145"/>
-      <c r="N79" s="146"/>
-      <c r="O79" s="147" t="s">
+      <c r="D79" s="187"/>
+      <c r="E79" s="187"/>
+      <c r="F79" s="187"/>
+      <c r="G79" s="187"/>
+      <c r="H79" s="187"/>
+      <c r="I79" s="187"/>
+      <c r="J79" s="187"/>
+      <c r="K79" s="187"/>
+      <c r="L79" s="187"/>
+      <c r="M79" s="187"/>
+      <c r="N79" s="188"/>
+      <c r="O79" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P79" s="148"/>
-      <c r="Q79" s="148"/>
-      <c r="R79" s="148"/>
-      <c r="S79" s="149"/>
-      <c r="T79" s="150" t="s">
+      <c r="P79" s="207"/>
+      <c r="Q79" s="207"/>
+      <c r="R79" s="207"/>
+      <c r="S79" s="208"/>
+      <c r="T79" s="186" t="s">
         <v>166</v>
       </c>
-      <c r="U79" s="145"/>
-      <c r="V79" s="145"/>
-      <c r="W79" s="146"/>
-      <c r="X79" s="150">
+      <c r="U79" s="187"/>
+      <c r="V79" s="187"/>
+      <c r="W79" s="188"/>
+      <c r="X79" s="186">
         <v>2</v>
       </c>
-      <c r="Y79" s="145"/>
-      <c r="Z79" s="146"/>
+      <c r="Y79" s="187"/>
+      <c r="Z79" s="188"/>
     </row>
     <row r="80" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A80" s="64" t="s">
@@ -7398,38 +7398,38 @@
       <c r="B80" s="64" t="s">
         <v>221</v>
       </c>
-      <c r="C80" s="144" t="s">
+      <c r="C80" s="203" t="s">
         <v>222</v>
       </c>
-      <c r="D80" s="145"/>
-      <c r="E80" s="145"/>
-      <c r="F80" s="145"/>
-      <c r="G80" s="145"/>
-      <c r="H80" s="145"/>
-      <c r="I80" s="145"/>
-      <c r="J80" s="145"/>
-      <c r="K80" s="145"/>
-      <c r="L80" s="145"/>
-      <c r="M80" s="145"/>
-      <c r="N80" s="146"/>
-      <c r="O80" s="147" t="s">
+      <c r="D80" s="187"/>
+      <c r="E80" s="187"/>
+      <c r="F80" s="187"/>
+      <c r="G80" s="187"/>
+      <c r="H80" s="187"/>
+      <c r="I80" s="187"/>
+      <c r="J80" s="187"/>
+      <c r="K80" s="187"/>
+      <c r="L80" s="187"/>
+      <c r="M80" s="187"/>
+      <c r="N80" s="188"/>
+      <c r="O80" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P80" s="148"/>
-      <c r="Q80" s="148"/>
-      <c r="R80" s="148"/>
-      <c r="S80" s="149"/>
-      <c r="T80" s="150" t="s">
+      <c r="P80" s="207"/>
+      <c r="Q80" s="207"/>
+      <c r="R80" s="207"/>
+      <c r="S80" s="208"/>
+      <c r="T80" s="186" t="s">
         <v>169</v>
       </c>
-      <c r="U80" s="145"/>
-      <c r="V80" s="145"/>
-      <c r="W80" s="146"/>
-      <c r="X80" s="150">
+      <c r="U80" s="187"/>
+      <c r="V80" s="187"/>
+      <c r="W80" s="188"/>
+      <c r="X80" s="186">
         <v>2</v>
       </c>
-      <c r="Y80" s="145"/>
-      <c r="Z80" s="146"/>
+      <c r="Y80" s="187"/>
+      <c r="Z80" s="188"/>
     </row>
     <row r="81" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A81" s="64" t="s">
@@ -7438,67 +7438,67 @@
       <c r="B81" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="C81" s="144" t="s">
+      <c r="C81" s="203" t="s">
         <v>224</v>
       </c>
-      <c r="D81" s="145"/>
-      <c r="E81" s="145"/>
-      <c r="F81" s="145"/>
-      <c r="G81" s="145"/>
-      <c r="H81" s="145"/>
-      <c r="I81" s="145"/>
-      <c r="J81" s="145"/>
-      <c r="K81" s="145"/>
-      <c r="L81" s="145"/>
-      <c r="M81" s="145"/>
-      <c r="N81" s="146"/>
-      <c r="O81" s="147" t="s">
+      <c r="D81" s="187"/>
+      <c r="E81" s="187"/>
+      <c r="F81" s="187"/>
+      <c r="G81" s="187"/>
+      <c r="H81" s="187"/>
+      <c r="I81" s="187"/>
+      <c r="J81" s="187"/>
+      <c r="K81" s="187"/>
+      <c r="L81" s="187"/>
+      <c r="M81" s="187"/>
+      <c r="N81" s="188"/>
+      <c r="O81" s="206" t="s">
         <v>146</v>
       </c>
-      <c r="P81" s="148"/>
-      <c r="Q81" s="148"/>
-      <c r="R81" s="148"/>
-      <c r="S81" s="149"/>
-      <c r="T81" s="150" t="s">
+      <c r="P81" s="207"/>
+      <c r="Q81" s="207"/>
+      <c r="R81" s="207"/>
+      <c r="S81" s="208"/>
+      <c r="T81" s="186" t="s">
         <v>172</v>
       </c>
-      <c r="U81" s="145"/>
-      <c r="V81" s="145"/>
-      <c r="W81" s="146"/>
-      <c r="X81" s="150">
+      <c r="U81" s="187"/>
+      <c r="V81" s="187"/>
+      <c r="W81" s="188"/>
+      <c r="X81" s="186">
         <v>2</v>
       </c>
-      <c r="Y81" s="145"/>
-      <c r="Z81" s="146"/>
+      <c r="Y81" s="187"/>
+      <c r="Z81" s="188"/>
     </row>
     <row r="82" spans="1:26" s="7" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="A82" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C82" s="151"/>
-      <c r="D82" s="151"/>
-      <c r="E82" s="151"/>
-      <c r="F82" s="151"/>
-      <c r="G82" s="151"/>
-      <c r="H82" s="151"/>
-      <c r="I82" s="151"/>
-      <c r="J82" s="151"/>
-      <c r="K82" s="151"/>
-      <c r="L82" s="151"/>
-      <c r="M82" s="151"/>
-      <c r="N82" s="151"/>
-      <c r="O82" s="151"/>
-      <c r="P82" s="151"/>
-      <c r="Q82" s="151"/>
-      <c r="R82" s="151"/>
-      <c r="S82" s="151"/>
-      <c r="T82" s="151"/>
-      <c r="U82" s="151"/>
-      <c r="V82" s="151"/>
-      <c r="W82" s="151"/>
-      <c r="X82" s="151"/>
-      <c r="Y82" s="151"/>
-      <c r="Z82" s="151"/>
+      <c r="C82" s="212"/>
+      <c r="D82" s="212"/>
+      <c r="E82" s="212"/>
+      <c r="F82" s="212"/>
+      <c r="G82" s="212"/>
+      <c r="H82" s="212"/>
+      <c r="I82" s="212"/>
+      <c r="J82" s="212"/>
+      <c r="K82" s="212"/>
+      <c r="L82" s="212"/>
+      <c r="M82" s="212"/>
+      <c r="N82" s="212"/>
+      <c r="O82" s="212"/>
+      <c r="P82" s="212"/>
+      <c r="Q82" s="212"/>
+      <c r="R82" s="212"/>
+      <c r="S82" s="212"/>
+      <c r="T82" s="212"/>
+      <c r="U82" s="212"/>
+      <c r="V82" s="212"/>
+      <c r="W82" s="212"/>
+      <c r="X82" s="212"/>
+      <c r="Y82" s="212"/>
+      <c r="Z82" s="212"/>
     </row>
     <row r="83" spans="1:26" ht="15.6">
       <c r="A83" s="67"/>
@@ -7530,37 +7530,221 @@
     </row>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A1:V5"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:H15"/>
-    <mergeCell ref="I14:N15"/>
-    <mergeCell ref="A6:Z6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="S9:V10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="O14:T15"/>
-    <mergeCell ref="U14:Z15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="C81:N81"/>
+    <mergeCell ref="O81:S81"/>
+    <mergeCell ref="T81:W81"/>
+    <mergeCell ref="X81:Z81"/>
+    <mergeCell ref="C82:N82"/>
+    <mergeCell ref="O82:S82"/>
+    <mergeCell ref="T82:W82"/>
+    <mergeCell ref="X82:Z82"/>
+    <mergeCell ref="C79:N79"/>
+    <mergeCell ref="O79:S79"/>
+    <mergeCell ref="T79:W79"/>
+    <mergeCell ref="X79:Z79"/>
+    <mergeCell ref="C80:N80"/>
+    <mergeCell ref="O80:S80"/>
+    <mergeCell ref="T80:W80"/>
+    <mergeCell ref="X80:Z80"/>
+    <mergeCell ref="X78:Z78"/>
+    <mergeCell ref="C75:N75"/>
+    <mergeCell ref="O75:S75"/>
+    <mergeCell ref="T75:W75"/>
+    <mergeCell ref="X75:Z75"/>
+    <mergeCell ref="C76:N76"/>
+    <mergeCell ref="O76:S76"/>
+    <mergeCell ref="T76:W76"/>
+    <mergeCell ref="X76:Z76"/>
+    <mergeCell ref="C77:N77"/>
+    <mergeCell ref="O77:S77"/>
+    <mergeCell ref="T77:W77"/>
+    <mergeCell ref="X77:Z77"/>
+    <mergeCell ref="C78:N78"/>
+    <mergeCell ref="O78:S78"/>
+    <mergeCell ref="T78:W78"/>
+    <mergeCell ref="C73:N73"/>
+    <mergeCell ref="O73:S73"/>
+    <mergeCell ref="T73:W73"/>
+    <mergeCell ref="X73:Z73"/>
+    <mergeCell ref="C74:N74"/>
+    <mergeCell ref="O74:S74"/>
+    <mergeCell ref="T74:W74"/>
+    <mergeCell ref="X74:Z74"/>
+    <mergeCell ref="C71:N71"/>
+    <mergeCell ref="O71:S71"/>
+    <mergeCell ref="T71:W71"/>
+    <mergeCell ref="X71:Z71"/>
+    <mergeCell ref="C72:N72"/>
+    <mergeCell ref="O72:S72"/>
+    <mergeCell ref="T72:W72"/>
+    <mergeCell ref="X72:Z72"/>
+    <mergeCell ref="C69:N69"/>
+    <mergeCell ref="O69:S69"/>
+    <mergeCell ref="T69:W69"/>
+    <mergeCell ref="X69:Z69"/>
+    <mergeCell ref="C70:N70"/>
+    <mergeCell ref="O70:S70"/>
+    <mergeCell ref="T70:W70"/>
+    <mergeCell ref="X70:Z70"/>
+    <mergeCell ref="C67:N67"/>
+    <mergeCell ref="O67:S67"/>
+    <mergeCell ref="T67:W67"/>
+    <mergeCell ref="X67:Z67"/>
+    <mergeCell ref="C68:N68"/>
+    <mergeCell ref="O68:S68"/>
+    <mergeCell ref="T68:W68"/>
+    <mergeCell ref="X68:Z68"/>
+    <mergeCell ref="C65:N65"/>
+    <mergeCell ref="O65:S65"/>
+    <mergeCell ref="T65:W65"/>
+    <mergeCell ref="X65:Z65"/>
+    <mergeCell ref="C66:N66"/>
+    <mergeCell ref="O66:S66"/>
+    <mergeCell ref="T66:W66"/>
+    <mergeCell ref="X66:Z66"/>
+    <mergeCell ref="C63:N63"/>
+    <mergeCell ref="O63:S63"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="X63:Z63"/>
+    <mergeCell ref="C64:N64"/>
+    <mergeCell ref="O64:S64"/>
+    <mergeCell ref="T64:W64"/>
+    <mergeCell ref="X64:Z64"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="C61:N61"/>
+    <mergeCell ref="O61:S61"/>
+    <mergeCell ref="T61:W61"/>
+    <mergeCell ref="X61:Z61"/>
+    <mergeCell ref="C62:N62"/>
+    <mergeCell ref="O62:S62"/>
+    <mergeCell ref="T62:W62"/>
+    <mergeCell ref="X62:Z62"/>
+    <mergeCell ref="C60:N60"/>
+    <mergeCell ref="O60:S60"/>
+    <mergeCell ref="T60:W60"/>
+    <mergeCell ref="X60:Z60"/>
+    <mergeCell ref="C57:N57"/>
+    <mergeCell ref="O57:S57"/>
+    <mergeCell ref="T57:W57"/>
+    <mergeCell ref="X57:Z57"/>
+    <mergeCell ref="C58:N58"/>
+    <mergeCell ref="O58:S58"/>
+    <mergeCell ref="T58:W58"/>
+    <mergeCell ref="X58:Z58"/>
+    <mergeCell ref="T56:W56"/>
+    <mergeCell ref="X56:Z56"/>
+    <mergeCell ref="C53:N53"/>
+    <mergeCell ref="O53:S53"/>
+    <mergeCell ref="T53:W53"/>
+    <mergeCell ref="X53:Z53"/>
+    <mergeCell ref="C59:N59"/>
+    <mergeCell ref="O59:S59"/>
+    <mergeCell ref="T59:W59"/>
+    <mergeCell ref="X59:Z59"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:N50"/>
+    <mergeCell ref="O50:S50"/>
+    <mergeCell ref="T50:W50"/>
+    <mergeCell ref="X50:Z50"/>
+    <mergeCell ref="C51:N51"/>
+    <mergeCell ref="O51:S51"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="C54:N54"/>
+    <mergeCell ref="O54:S54"/>
+    <mergeCell ref="T54:W54"/>
+    <mergeCell ref="X54:Z54"/>
+    <mergeCell ref="C55:N55"/>
+    <mergeCell ref="T51:W51"/>
+    <mergeCell ref="X51:Z51"/>
+    <mergeCell ref="C52:N52"/>
+    <mergeCell ref="O52:S52"/>
+    <mergeCell ref="T52:W52"/>
+    <mergeCell ref="X52:Z52"/>
+    <mergeCell ref="O55:S55"/>
+    <mergeCell ref="T55:W55"/>
+    <mergeCell ref="X55:Z55"/>
+    <mergeCell ref="C56:N56"/>
+    <mergeCell ref="O56:S56"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="C48:N48"/>
+    <mergeCell ref="O48:S48"/>
+    <mergeCell ref="T48:W48"/>
+    <mergeCell ref="X48:Z48"/>
+    <mergeCell ref="C49:N49"/>
+    <mergeCell ref="O49:S49"/>
+    <mergeCell ref="T49:W49"/>
+    <mergeCell ref="X49:Z49"/>
+    <mergeCell ref="O45:S45"/>
+    <mergeCell ref="T45:W45"/>
+    <mergeCell ref="X45:Z45"/>
+    <mergeCell ref="C46:N46"/>
+    <mergeCell ref="O46:S46"/>
+    <mergeCell ref="T46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="C43:N43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="T43:W43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="C44:N44"/>
+    <mergeCell ref="O44:S44"/>
+    <mergeCell ref="T44:W44"/>
+    <mergeCell ref="X44:Z44"/>
+    <mergeCell ref="C45:N45"/>
+    <mergeCell ref="C47:N47"/>
+    <mergeCell ref="O47:S47"/>
+    <mergeCell ref="T47:W47"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="C42:N42"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="T42:W42"/>
+    <mergeCell ref="X42:Z42"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="O24:T24"/>
+    <mergeCell ref="U24:Z24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="O25:T25"/>
+    <mergeCell ref="U25:Z25"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="I24:N24"/>
@@ -7585,221 +7769,37 @@
     <mergeCell ref="U17:Z17"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="I18:N18"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="O24:T24"/>
-    <mergeCell ref="U24:Z24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="O25:T25"/>
-    <mergeCell ref="U25:Z25"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="T42:W42"/>
-    <mergeCell ref="X42:Z42"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="O45:S45"/>
-    <mergeCell ref="T45:W45"/>
-    <mergeCell ref="X45:Z45"/>
-    <mergeCell ref="C46:N46"/>
-    <mergeCell ref="O46:S46"/>
-    <mergeCell ref="T46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="C43:N43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="T43:W43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="C44:N44"/>
-    <mergeCell ref="O44:S44"/>
-    <mergeCell ref="T44:W44"/>
-    <mergeCell ref="X44:Z44"/>
-    <mergeCell ref="C45:N45"/>
-    <mergeCell ref="C47:N47"/>
-    <mergeCell ref="O47:S47"/>
-    <mergeCell ref="T47:W47"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="C48:N48"/>
-    <mergeCell ref="O48:S48"/>
-    <mergeCell ref="T48:W48"/>
-    <mergeCell ref="X48:Z48"/>
-    <mergeCell ref="C49:N49"/>
-    <mergeCell ref="O49:S49"/>
-    <mergeCell ref="T49:W49"/>
-    <mergeCell ref="X49:Z49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="C50:N50"/>
-    <mergeCell ref="O50:S50"/>
-    <mergeCell ref="T50:W50"/>
-    <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="C51:N51"/>
-    <mergeCell ref="O51:S51"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="C54:N54"/>
-    <mergeCell ref="O54:S54"/>
-    <mergeCell ref="T54:W54"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="C55:N55"/>
-    <mergeCell ref="T51:W51"/>
-    <mergeCell ref="X51:Z51"/>
-    <mergeCell ref="C52:N52"/>
-    <mergeCell ref="O52:S52"/>
-    <mergeCell ref="T52:W52"/>
-    <mergeCell ref="X52:Z52"/>
-    <mergeCell ref="O55:S55"/>
-    <mergeCell ref="T55:W55"/>
-    <mergeCell ref="X55:Z55"/>
-    <mergeCell ref="C56:N56"/>
-    <mergeCell ref="O56:S56"/>
-    <mergeCell ref="T56:W56"/>
-    <mergeCell ref="X56:Z56"/>
-    <mergeCell ref="C53:N53"/>
-    <mergeCell ref="O53:S53"/>
-    <mergeCell ref="T53:W53"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="C59:N59"/>
-    <mergeCell ref="O59:S59"/>
-    <mergeCell ref="T59:W59"/>
-    <mergeCell ref="X59:Z59"/>
-    <mergeCell ref="C60:N60"/>
-    <mergeCell ref="O60:S60"/>
-    <mergeCell ref="T60:W60"/>
-    <mergeCell ref="X60:Z60"/>
-    <mergeCell ref="C57:N57"/>
-    <mergeCell ref="O57:S57"/>
-    <mergeCell ref="T57:W57"/>
-    <mergeCell ref="X57:Z57"/>
-    <mergeCell ref="C58:N58"/>
-    <mergeCell ref="O58:S58"/>
-    <mergeCell ref="T58:W58"/>
-    <mergeCell ref="X58:Z58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="C61:N61"/>
-    <mergeCell ref="O61:S61"/>
-    <mergeCell ref="T61:W61"/>
-    <mergeCell ref="X61:Z61"/>
-    <mergeCell ref="C62:N62"/>
-    <mergeCell ref="O62:S62"/>
-    <mergeCell ref="T62:W62"/>
-    <mergeCell ref="X62:Z62"/>
-    <mergeCell ref="C65:N65"/>
-    <mergeCell ref="O65:S65"/>
-    <mergeCell ref="T65:W65"/>
-    <mergeCell ref="X65:Z65"/>
-    <mergeCell ref="C66:N66"/>
-    <mergeCell ref="O66:S66"/>
-    <mergeCell ref="T66:W66"/>
-    <mergeCell ref="X66:Z66"/>
-    <mergeCell ref="C63:N63"/>
-    <mergeCell ref="O63:S63"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="X63:Z63"/>
-    <mergeCell ref="C64:N64"/>
-    <mergeCell ref="O64:S64"/>
-    <mergeCell ref="T64:W64"/>
-    <mergeCell ref="X64:Z64"/>
-    <mergeCell ref="C69:N69"/>
-    <mergeCell ref="O69:S69"/>
-    <mergeCell ref="T69:W69"/>
-    <mergeCell ref="X69:Z69"/>
-    <mergeCell ref="C70:N70"/>
-    <mergeCell ref="O70:S70"/>
-    <mergeCell ref="T70:W70"/>
-    <mergeCell ref="X70:Z70"/>
-    <mergeCell ref="C67:N67"/>
-    <mergeCell ref="O67:S67"/>
-    <mergeCell ref="T67:W67"/>
-    <mergeCell ref="X67:Z67"/>
-    <mergeCell ref="C68:N68"/>
-    <mergeCell ref="O68:S68"/>
-    <mergeCell ref="T68:W68"/>
-    <mergeCell ref="X68:Z68"/>
-    <mergeCell ref="C73:N73"/>
-    <mergeCell ref="O73:S73"/>
-    <mergeCell ref="T73:W73"/>
-    <mergeCell ref="X73:Z73"/>
-    <mergeCell ref="C74:N74"/>
-    <mergeCell ref="O74:S74"/>
-    <mergeCell ref="T74:W74"/>
-    <mergeCell ref="X74:Z74"/>
-    <mergeCell ref="C71:N71"/>
-    <mergeCell ref="O71:S71"/>
-    <mergeCell ref="T71:W71"/>
-    <mergeCell ref="X71:Z71"/>
-    <mergeCell ref="C72:N72"/>
-    <mergeCell ref="O72:S72"/>
-    <mergeCell ref="T72:W72"/>
-    <mergeCell ref="X72:Z72"/>
-    <mergeCell ref="X78:Z78"/>
-    <mergeCell ref="C75:N75"/>
-    <mergeCell ref="O75:S75"/>
-    <mergeCell ref="T75:W75"/>
-    <mergeCell ref="X75:Z75"/>
-    <mergeCell ref="C76:N76"/>
-    <mergeCell ref="O76:S76"/>
-    <mergeCell ref="T76:W76"/>
-    <mergeCell ref="X76:Z76"/>
-    <mergeCell ref="C77:N77"/>
-    <mergeCell ref="O77:S77"/>
-    <mergeCell ref="T77:W77"/>
-    <mergeCell ref="X77:Z77"/>
-    <mergeCell ref="C78:N78"/>
-    <mergeCell ref="O78:S78"/>
-    <mergeCell ref="T78:W78"/>
-    <mergeCell ref="C81:N81"/>
-    <mergeCell ref="O81:S81"/>
-    <mergeCell ref="T81:W81"/>
-    <mergeCell ref="X81:Z81"/>
-    <mergeCell ref="C82:N82"/>
-    <mergeCell ref="O82:S82"/>
-    <mergeCell ref="T82:W82"/>
-    <mergeCell ref="X82:Z82"/>
-    <mergeCell ref="C79:N79"/>
-    <mergeCell ref="O79:S79"/>
-    <mergeCell ref="T79:W79"/>
-    <mergeCell ref="X79:Z79"/>
-    <mergeCell ref="C80:N80"/>
-    <mergeCell ref="O80:S80"/>
-    <mergeCell ref="T80:W80"/>
-    <mergeCell ref="X80:Z80"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="O14:T15"/>
+    <mergeCell ref="U14:Z15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="A1:V5"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:H15"/>
+    <mergeCell ref="I14:N15"/>
+    <mergeCell ref="A6:Z6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="S9:V10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G7:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7819,194 +7819,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
       <c r="W1" s="56"/>
       <c r="X1" s="56"/>
       <c r="Y1" s="56"/>
       <c r="Z1" s="56"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="201"/>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="201"/>
-      <c r="K2" s="201"/>
-      <c r="L2" s="201"/>
-      <c r="M2" s="201"/>
-      <c r="N2" s="201"/>
-      <c r="O2" s="201"/>
-      <c r="P2" s="201"/>
-      <c r="Q2" s="201"/>
-      <c r="R2" s="201"/>
-      <c r="S2" s="201"/>
-      <c r="T2" s="201"/>
-      <c r="U2" s="201"/>
-      <c r="V2" s="201"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
       <c r="W2" s="56"/>
       <c r="X2" s="56"/>
       <c r="Y2" s="56"/>
       <c r="Z2" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="201"/>
-      <c r="B3" s="201"/>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
-      <c r="L3" s="201"/>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
-      <c r="Q3" s="201"/>
-      <c r="R3" s="201"/>
-      <c r="S3" s="201"/>
-      <c r="T3" s="201"/>
-      <c r="U3" s="201"/>
-      <c r="V3" s="201"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="144"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="144"/>
+      <c r="S3" s="144"/>
+      <c r="T3" s="144"/>
+      <c r="U3" s="144"/>
+      <c r="V3" s="144"/>
       <c r="W3" s="56"/>
       <c r="X3" s="56"/>
       <c r="Y3" s="56"/>
       <c r="Z3" s="56"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="201"/>
-      <c r="B4" s="201"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="M4" s="201"/>
-      <c r="N4" s="201"/>
-      <c r="O4" s="201"/>
-      <c r="P4" s="201"/>
-      <c r="Q4" s="201"/>
-      <c r="R4" s="201"/>
-      <c r="S4" s="201"/>
-      <c r="T4" s="201"/>
-      <c r="U4" s="201"/>
-      <c r="V4" s="201"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="144"/>
+      <c r="Q4" s="144"/>
+      <c r="R4" s="144"/>
+      <c r="S4" s="144"/>
+      <c r="T4" s="144"/>
+      <c r="U4" s="144"/>
+      <c r="V4" s="144"/>
       <c r="W4" s="56"/>
       <c r="X4" s="56"/>
       <c r="Y4" s="56"/>
       <c r="Z4" s="56"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="201"/>
-      <c r="R5" s="201"/>
-      <c r="S5" s="201"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="201"/>
-      <c r="V5" s="201"/>
+      <c r="A5" s="144"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
+      <c r="R5" s="144"/>
+      <c r="S5" s="144"/>
+      <c r="T5" s="144"/>
+      <c r="U5" s="144"/>
+      <c r="V5" s="144"/>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="56"/>
       <c r="Z5" s="56"/>
     </row>
     <row r="6" spans="1:26" ht="30">
-      <c r="A6" s="209" t="s">
+      <c r="A6" s="153" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="209"/>
-      <c r="C6" s="209"/>
-      <c r="D6" s="209"/>
-      <c r="E6" s="209"/>
-      <c r="F6" s="209"/>
-      <c r="G6" s="209"/>
-      <c r="H6" s="209"/>
-      <c r="I6" s="209"/>
-      <c r="J6" s="209"/>
-      <c r="K6" s="209"/>
-      <c r="L6" s="209"/>
-      <c r="M6" s="209"/>
-      <c r="N6" s="209"/>
-      <c r="O6" s="209"/>
-      <c r="P6" s="209"/>
-      <c r="Q6" s="209"/>
-      <c r="R6" s="209"/>
-      <c r="S6" s="209"/>
-      <c r="T6" s="209"/>
-      <c r="U6" s="209"/>
-      <c r="V6" s="209"/>
-      <c r="W6" s="209"/>
-      <c r="X6" s="209"/>
-      <c r="Y6" s="209"/>
-      <c r="Z6" s="209"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153"/>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
+      <c r="W6" s="153"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
     </row>
     <row r="7" spans="1:26" s="7" customFormat="1" ht="17.399999999999999">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="154" t="s">
         <v>225</v>
       </c>
-      <c r="B7" s="210"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="55" t="s">
         <v>81</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
-      <c r="G7" s="212" t="str">
+      <c r="G7" s="156" t="str">
         <f>'ใบงาน Agilent_JOB 2.1'!F7</f>
         <v>xxxx</v>
       </c>
-      <c r="H7" s="212"/>
-      <c r="I7" s="212"/>
-      <c r="J7" s="212"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
@@ -8039,13 +8039,13 @@
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
       <c r="F8" s="48"/>
-      <c r="G8" s="211" t="str">
+      <c r="G8" s="155" t="str">
         <f>'ใบงาน Agilent_JOB 2.1'!F9</f>
         <v>K9801-60082</v>
       </c>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="211"/>
+      <c r="H8" s="155"/>
+      <c r="I8" s="155"/>
+      <c r="J8" s="155"/>
       <c r="K8" s="54"/>
       <c r="L8" s="54"/>
       <c r="M8" s="54"/>
@@ -8066,21 +8066,21 @@
       </c>
     </row>
     <row r="9" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="A9" s="214" t="s">
+      <c r="A9" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="214"/>
+      <c r="B9" s="213"/>
       <c r="C9" s="47"/>
       <c r="D9" s="47"/>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
-      <c r="G9" s="211" t="str">
+      <c r="G9" s="155" t="str">
         <f>'ใบงาน Agilent_JOB 2.2'!F9</f>
         <v>K9801-60083</v>
       </c>
-      <c r="H9" s="211"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="211"/>
+      <c r="H9" s="155"/>
+      <c r="I9" s="155"/>
+      <c r="J9" s="155"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
@@ -8098,17 +8098,17 @@
         <v>90</v>
       </c>
       <c r="C10" s="17"/>
-      <c r="D10" s="212" t="s">
+      <c r="D10" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="202" t="s">
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
       <c r="K10" s="55"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
@@ -8119,17 +8119,17 @@
       <c r="R10" s="17"/>
     </row>
     <row r="11" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="B11" s="212"/>
+      <c r="B11" s="156"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
-      <c r="G11" s="202" t="s">
+      <c r="G11" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="202"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="202"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
@@ -8138,28 +8138,28 @@
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="129" t="s">
+      <c r="S11" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="T11" s="129"/>
-      <c r="U11" s="129"/>
-      <c r="V11" s="129"/>
+      <c r="T11" s="99"/>
+      <c r="U11" s="99"/>
+      <c r="V11" s="99"/>
     </row>
     <row r="12" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A12" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="B12" s="212"/>
+      <c r="B12" s="156"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="202" t="s">
+      <c r="G12" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="202"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="202"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -8168,14 +8168,14 @@
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="129"/>
-      <c r="T12" s="129"/>
-      <c r="U12" s="129"/>
-      <c r="V12" s="129"/>
+      <c r="S12" s="99"/>
+      <c r="T12" s="99"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="99"/>
     </row>
     <row r="13" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A13" s="17"/>
-      <c r="B13" s="213"/>
+      <c r="B13" s="214"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
@@ -8196,224 +8196,224 @@
       <c r="T13" s="17"/>
     </row>
     <row r="14" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="A14" s="203" t="s">
+      <c r="A14" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="203" t="s">
+      <c r="B14" s="146" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="194" t="s">
+      <c r="C14" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="194" t="s">
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="204"/>
-      <c r="K14" s="204"/>
-      <c r="L14" s="204"/>
-      <c r="M14" s="204"/>
-      <c r="N14" s="205"/>
-      <c r="O14" s="194" t="s">
+      <c r="J14" s="148"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="148"/>
+      <c r="M14" s="148"/>
+      <c r="N14" s="149"/>
+      <c r="O14" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="195"/>
-      <c r="S14" s="195"/>
-      <c r="T14" s="196"/>
-      <c r="U14" s="200" t="s">
+      <c r="P14" s="158"/>
+      <c r="Q14" s="158"/>
+      <c r="R14" s="158"/>
+      <c r="S14" s="158"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="163" t="s">
         <v>89</v>
       </c>
-      <c r="V14" s="200"/>
-      <c r="W14" s="200"/>
-      <c r="X14" s="200"/>
-      <c r="Y14" s="200"/>
-      <c r="Z14" s="200"/>
+      <c r="V14" s="163"/>
+      <c r="W14" s="163"/>
+      <c r="X14" s="163"/>
+      <c r="Y14" s="163"/>
+      <c r="Z14" s="163"/>
     </row>
     <row r="15" spans="1:26" s="7" customFormat="1" ht="13.8">
-      <c r="A15" s="121"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="207"/>
-      <c r="H15" s="208"/>
-      <c r="I15" s="206"/>
-      <c r="J15" s="207"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="208"/>
-      <c r="O15" s="197"/>
-      <c r="P15" s="198"/>
-      <c r="Q15" s="198"/>
-      <c r="R15" s="198"/>
-      <c r="S15" s="198"/>
-      <c r="T15" s="199"/>
-      <c r="U15" s="200"/>
-      <c r="V15" s="200"/>
-      <c r="W15" s="200"/>
-      <c r="X15" s="200"/>
-      <c r="Y15" s="200"/>
-      <c r="Z15" s="200"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="151"/>
+      <c r="M15" s="151"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="160"/>
+      <c r="P15" s="161"/>
+      <c r="Q15" s="161"/>
+      <c r="R15" s="161"/>
+      <c r="S15" s="161"/>
+      <c r="T15" s="162"/>
+      <c r="U15" s="163"/>
+      <c r="V15" s="163"/>
+      <c r="W15" s="163"/>
+      <c r="X15" s="163"/>
+      <c r="Y15" s="163"/>
+      <c r="Z15" s="163"/>
     </row>
     <row r="16" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
-      <c r="A16" s="190">
+      <c r="A16" s="164">
         <v>1</v>
       </c>
       <c r="B16" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-      <c r="F16" s="189"/>
-      <c r="G16" s="189"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="189"/>
-      <c r="J16" s="189"/>
-      <c r="K16" s="189"/>
-      <c r="L16" s="189"/>
-      <c r="M16" s="189"/>
-      <c r="N16" s="189"/>
-      <c r="O16" s="189"/>
-      <c r="P16" s="189"/>
-      <c r="Q16" s="189"/>
-      <c r="R16" s="189"/>
-      <c r="S16" s="189"/>
-      <c r="T16" s="189"/>
-      <c r="U16" s="189"/>
-      <c r="V16" s="189"/>
-      <c r="W16" s="189"/>
-      <c r="X16" s="189"/>
-      <c r="Y16" s="189"/>
-      <c r="Z16" s="189"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="157"/>
+      <c r="J16" s="157"/>
+      <c r="K16" s="157"/>
+      <c r="L16" s="157"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="157"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="157"/>
+      <c r="Q16" s="157"/>
+      <c r="R16" s="157"/>
+      <c r="S16" s="157"/>
+      <c r="T16" s="157"/>
+      <c r="U16" s="157"/>
+      <c r="V16" s="157"/>
+      <c r="W16" s="157"/>
+      <c r="X16" s="157"/>
+      <c r="Y16" s="157"/>
+      <c r="Z16" s="157"/>
     </row>
     <row r="17" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
-      <c r="A17" s="191"/>
+      <c r="A17" s="165"/>
       <c r="B17" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="189"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="189"/>
-      <c r="H17" s="189"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="189"/>
-      <c r="L17" s="189"/>
-      <c r="M17" s="189"/>
-      <c r="N17" s="189"/>
-      <c r="O17" s="189"/>
-      <c r="P17" s="189"/>
-      <c r="Q17" s="189"/>
-      <c r="R17" s="189"/>
-      <c r="S17" s="189"/>
-      <c r="T17" s="189"/>
-      <c r="U17" s="189"/>
-      <c r="V17" s="189"/>
-      <c r="W17" s="189"/>
-      <c r="X17" s="189"/>
-      <c r="Y17" s="189"/>
-      <c r="Z17" s="189"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="157"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="157"/>
+      <c r="Q17" s="157"/>
+      <c r="R17" s="157"/>
+      <c r="S17" s="157"/>
+      <c r="T17" s="157"/>
+      <c r="U17" s="157"/>
+      <c r="V17" s="157"/>
+      <c r="W17" s="157"/>
+      <c r="X17" s="157"/>
+      <c r="Y17" s="157"/>
+      <c r="Z17" s="157"/>
     </row>
     <row r="18" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
-      <c r="A18" s="191"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="189"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="189"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="189"/>
-      <c r="L18" s="189"/>
-      <c r="M18" s="189"/>
-      <c r="N18" s="189"/>
-      <c r="O18" s="189"/>
-      <c r="P18" s="189"/>
-      <c r="Q18" s="189"/>
-      <c r="R18" s="189"/>
-      <c r="S18" s="189"/>
-      <c r="T18" s="189"/>
-      <c r="U18" s="189"/>
-      <c r="V18" s="189"/>
-      <c r="W18" s="189"/>
-      <c r="X18" s="189"/>
-      <c r="Y18" s="189"/>
-      <c r="Z18" s="189"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="157"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="157"/>
+      <c r="N18" s="157"/>
+      <c r="O18" s="157"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="157"/>
+      <c r="S18" s="157"/>
+      <c r="T18" s="157"/>
+      <c r="U18" s="157"/>
+      <c r="V18" s="157"/>
+      <c r="W18" s="157"/>
+      <c r="X18" s="157"/>
+      <c r="Y18" s="157"/>
+      <c r="Z18" s="157"/>
     </row>
     <row r="19" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
-      <c r="A19" s="191"/>
+      <c r="A19" s="165"/>
       <c r="B19" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="189"/>
-      <c r="D19" s="189"/>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="189"/>
-      <c r="H19" s="189"/>
-      <c r="I19" s="189"/>
-      <c r="J19" s="189"/>
-      <c r="K19" s="189"/>
-      <c r="L19" s="189"/>
-      <c r="M19" s="189"/>
-      <c r="N19" s="189"/>
-      <c r="O19" s="189"/>
-      <c r="P19" s="189"/>
-      <c r="Q19" s="189"/>
-      <c r="R19" s="189"/>
-      <c r="S19" s="189"/>
-      <c r="T19" s="189"/>
-      <c r="U19" s="189"/>
-      <c r="V19" s="189"/>
-      <c r="W19" s="189"/>
-      <c r="X19" s="189"/>
-      <c r="Y19" s="189"/>
-      <c r="Z19" s="189"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="157"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="157"/>
+      <c r="K19" s="157"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="157"/>
+      <c r="O19" s="157"/>
+      <c r="P19" s="157"/>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="157"/>
+      <c r="S19" s="157"/>
+      <c r="T19" s="157"/>
+      <c r="U19" s="157"/>
+      <c r="V19" s="157"/>
+      <c r="W19" s="157"/>
+      <c r="X19" s="157"/>
+      <c r="Y19" s="157"/>
+      <c r="Z19" s="157"/>
     </row>
     <row r="20" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
-      <c r="A20" s="192"/>
+      <c r="A20" s="166"/>
       <c r="B20" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="189"/>
-      <c r="D20" s="189"/>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="189"/>
-      <c r="L20" s="189"/>
-      <c r="M20" s="189"/>
-      <c r="N20" s="189"/>
-      <c r="O20" s="189"/>
-      <c r="P20" s="189"/>
-      <c r="Q20" s="189"/>
-      <c r="R20" s="189"/>
-      <c r="S20" s="189"/>
-      <c r="T20" s="189"/>
-      <c r="U20" s="189"/>
-      <c r="V20" s="189"/>
-      <c r="W20" s="189"/>
-      <c r="X20" s="189"/>
-      <c r="Y20" s="189"/>
-      <c r="Z20" s="189"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="157"/>
+      <c r="I20" s="157"/>
+      <c r="J20" s="157"/>
+      <c r="K20" s="157"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="157"/>
+      <c r="O20" s="157"/>
+      <c r="P20" s="157"/>
+      <c r="Q20" s="157"/>
+      <c r="R20" s="157"/>
+      <c r="S20" s="157"/>
+      <c r="T20" s="157"/>
+      <c r="U20" s="157"/>
+      <c r="V20" s="157"/>
+      <c r="W20" s="157"/>
+      <c r="X20" s="157"/>
+      <c r="Y20" s="157"/>
+      <c r="Z20" s="157"/>
     </row>
     <row r="21" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
       <c r="A21" s="58">
@@ -8422,30 +8422,30 @@
       <c r="B21" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="189"/>
-      <c r="D21" s="189"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="189"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="189"/>
-      <c r="L21" s="189"/>
-      <c r="M21" s="189"/>
-      <c r="N21" s="189"/>
-      <c r="O21" s="189"/>
-      <c r="P21" s="189"/>
-      <c r="Q21" s="189"/>
-      <c r="R21" s="189"/>
-      <c r="S21" s="189"/>
-      <c r="T21" s="189"/>
-      <c r="U21" s="189"/>
-      <c r="V21" s="189"/>
-      <c r="W21" s="189"/>
-      <c r="X21" s="189"/>
-      <c r="Y21" s="189"/>
-      <c r="Z21" s="189"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="157"/>
+      <c r="I21" s="157"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="157"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="157"/>
+      <c r="S21" s="157"/>
+      <c r="T21" s="157"/>
+      <c r="U21" s="157"/>
+      <c r="V21" s="157"/>
+      <c r="W21" s="157"/>
+      <c r="X21" s="157"/>
+      <c r="Y21" s="157"/>
+      <c r="Z21" s="157"/>
     </row>
     <row r="22" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
       <c r="A22" s="58">
@@ -8454,30 +8454,30 @@
       <c r="B22" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="C22" s="189"/>
-      <c r="D22" s="189"/>
-      <c r="E22" s="189"/>
-      <c r="F22" s="189"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="189"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="189"/>
-      <c r="L22" s="189"/>
-      <c r="M22" s="189"/>
-      <c r="N22" s="189"/>
-      <c r="O22" s="189"/>
-      <c r="P22" s="189"/>
-      <c r="Q22" s="189"/>
-      <c r="R22" s="189"/>
-      <c r="S22" s="189"/>
-      <c r="T22" s="189"/>
-      <c r="U22" s="189"/>
-      <c r="V22" s="189"/>
-      <c r="W22" s="189"/>
-      <c r="X22" s="189"/>
-      <c r="Y22" s="189"/>
-      <c r="Z22" s="189"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="157"/>
+      <c r="O22" s="157"/>
+      <c r="P22" s="157"/>
+      <c r="Q22" s="157"/>
+      <c r="R22" s="157"/>
+      <c r="S22" s="157"/>
+      <c r="T22" s="157"/>
+      <c r="U22" s="157"/>
+      <c r="V22" s="157"/>
+      <c r="W22" s="157"/>
+      <c r="X22" s="157"/>
+      <c r="Y22" s="157"/>
+      <c r="Z22" s="157"/>
     </row>
     <row r="23" spans="1:26" s="60" customFormat="1" ht="17.399999999999999">
       <c r="A23" s="58">
@@ -8486,101 +8486,60 @@
       <c r="B23" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="189"/>
-      <c r="D23" s="189"/>
-      <c r="E23" s="189"/>
-      <c r="F23" s="189"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="189"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="189"/>
-      <c r="K23" s="189"/>
-      <c r="L23" s="189"/>
-      <c r="M23" s="189"/>
-      <c r="N23" s="189"/>
-      <c r="O23" s="189"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="189"/>
-      <c r="T23" s="189"/>
-      <c r="U23" s="189"/>
-      <c r="V23" s="189"/>
-      <c r="W23" s="189"/>
-      <c r="X23" s="189"/>
-      <c r="Y23" s="189"/>
-      <c r="Z23" s="189"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="157"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="157"/>
+      <c r="O23" s="157"/>
+      <c r="P23" s="157"/>
+      <c r="Q23" s="157"/>
+      <c r="R23" s="157"/>
+      <c r="S23" s="157"/>
+      <c r="T23" s="157"/>
+      <c r="U23" s="157"/>
+      <c r="V23" s="157"/>
+      <c r="W23" s="157"/>
+      <c r="X23" s="157"/>
+      <c r="Y23" s="157"/>
+      <c r="Z23" s="157"/>
     </row>
     <row r="24" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A24" s="6"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
     </row>
     <row r="25" spans="1:26" s="62" customFormat="1" ht="15">
       <c r="A25" s="63"/>
-      <c r="L25" s="183"/>
-      <c r="M25" s="183"/>
+      <c r="L25" s="176"/>
+      <c r="M25" s="176"/>
     </row>
     <row r="26" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A26" s="6"/>
-      <c r="L26" s="171"/>
-      <c r="M26" s="171"/>
+      <c r="L26" s="167"/>
+      <c r="M26" s="167"/>
     </row>
     <row r="27" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A27" s="6"/>
-      <c r="L27" s="171"/>
-      <c r="M27" s="171"/>
+      <c r="L27" s="167"/>
+      <c r="M27" s="167"/>
     </row>
     <row r="28" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A28" s="6"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="171"/>
+      <c r="L28" s="167"/>
+      <c r="M28" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A1:V5"/>
-    <mergeCell ref="A6:Z6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="S11:V12"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:H15"/>
-    <mergeCell ref="I14:N15"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="U23:Z23"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="U22:Z22"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="O14:T15"/>
@@ -8597,6 +8556,47 @@
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="I23:N23"/>
     <mergeCell ref="O23:T23"/>
+    <mergeCell ref="U23:Z23"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:H15"/>
+    <mergeCell ref="I14:N15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="S11:V12"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="A1:V5"/>
+    <mergeCell ref="A6:Z6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
